--- a/data-raw/Rolodex.xlsx
+++ b/data-raw/Rolodex.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EO276194\Desktop\Rolodex\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JG979646\Desktop\Rolodex\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF0C386-5CB8-449D-85F6-7F99A661BC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA11D5F1-3D87-4D28-860C-3C62EEA563EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rolodex NEW" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="611">
   <si>
     <t>Name</t>
   </si>
@@ -1921,6 +1921,24 @@
   </si>
   <si>
     <t>Hotlines</t>
+  </si>
+  <si>
+    <t>Joe's Resource</t>
+  </si>
+  <si>
+    <t>1800 Penn Ave</t>
+  </si>
+  <si>
+    <t>tel:5555555555</t>
+  </si>
+  <si>
+    <t>https://google.com</t>
+  </si>
+  <si>
+    <t>M-F: 9:00 AM - 9:00 PM</t>
+  </si>
+  <si>
+    <t>A new Sexual Health Resource on campus as of June 2026</t>
   </si>
 </sst>
 </file>
@@ -2499,7 +2517,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2534,6 +2552,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="42" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2890,16 +2909,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I169"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I171"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="88.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="43.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="96.28515625" style="2" customWidth="1"/>
-    <col min="5" max="8" width="25.140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="78.140625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.7109375" style="2"/>
+    <col min="1" max="1" width="88.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="96.33203125" style="2" customWidth="1"/>
+    <col min="5" max="8" width="25.109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="78.109375" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2933,80 +2952,76 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>118</v>
+        <v>605</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>119</v>
+        <v>606</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>607</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>608</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>120</v>
-      </c>
+        <v>609</v>
+      </c>
+      <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>156</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>605</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>28</v>
+        <v>606</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>607</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>608</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>609</v>
+      </c>
+      <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>159</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>118</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>590</v>
@@ -3015,27 +3030,27 @@
         <v>24</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>513</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>161</v>
+        <v>318</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>590</v>
@@ -3044,25 +3059,27 @@
         <v>24</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>514</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="1"/>
+        <v>258</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="F6" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>590</v>
@@ -3071,25 +3088,27 @@
         <v>24</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>513</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="F7" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>590</v>
@@ -3098,12 +3117,12 @@
         <v>24</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>251</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>130</v>
@@ -3112,11 +3131,11 @@
         <v>260</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>590</v>
@@ -3125,27 +3144,25 @@
         <v>24</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>164</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>590</v>
@@ -3154,75 +3171,97 @@
         <v>24</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>165</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="2" t="s">
+      <c r="B12" s="1"/>
+      <c r="C12" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="1" customFormat="1">
-      <c r="A11" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="1" customFormat="1">
-      <c r="A12" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>369</v>
-      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
         <v>592</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>370</v>
+      <c r="I12" s="1" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="1" customFormat="1">
       <c r="A13" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>366</v>
+        <v>47</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>592</v>
@@ -3230,95 +3269,84 @@
       <c r="H13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I13" s="12" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="I13" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="1" customFormat="1">
       <c r="A14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="2" t="s">
-        <v>316</v>
+        <v>368</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1" t="s">
-        <v>50</v>
+        <v>369</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>592</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>8</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="1" customFormat="1">
       <c r="A15" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>263</v>
+        <v>365</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+        <v>366</v>
+      </c>
       <c r="G15" s="1" t="s">
         <v>592</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>169</v>
+      <c r="I15" s="12" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>304</v>
+        <v>48</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="2" t="s">
+        <v>316</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="G16" s="1" t="s">
         <v>592</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>320</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
         <v>592</v>
       </c>
@@ -3326,70 +3354,57 @@
         <v>8</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>321</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>122</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>264</v>
+        <v>138</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>304</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>53</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
       <c r="G18" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>53</v>
+        <v>319</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>320</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>174</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>130</v>
@@ -3413,12 +3428,12 @@
         <v>24</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>130</v>
@@ -3442,12 +3457,12 @@
         <v>24</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>130</v>
@@ -3471,85 +3486,85 @@
         <v>24</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="1" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>293</v>
+        <v>264</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>178</v>
+        <v>161</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>58</v>
+        <v>265</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>293</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>593</v>
@@ -3558,25 +3573,27 @@
         <v>24</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E26" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>180</v>
+      </c>
       <c r="F26" s="1" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>593</v>
@@ -3585,61 +3602,74 @@
         <v>24</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>252</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>331</v>
+        <v>56</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>332</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>195</v>
+        <v>59</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
+      <c r="F28" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="G28" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>196</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>334</v>
+        <v>330</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>594</v>
@@ -3648,32 +3678,41 @@
         <v>8</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>337</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
         <v>594</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>338</v>
+      <c r="I30" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>340</v>
+        <v>346</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>334</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>594</v>
@@ -3681,103 +3720,81 @@
       <c r="H31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I31" s="14" t="s">
-        <v>341</v>
+      <c r="I31" s="1" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="2" t="s">
-        <v>342</v>
+      <c r="A32" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="G32" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>345</v>
+      <c r="H32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F33" s="1"/>
+        <v>339</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>340</v>
+      </c>
       <c r="G33" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>185</v>
+      <c r="I33" s="14" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="H34" s="1" t="s">
+      <c r="A34" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>186</v>
+        <v>345</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="1" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
         <v>595</v>
       </c>
@@ -3785,24 +3802,28 @@
         <v>8</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>313</v>
+        <v>141</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="G36" s="1" t="s">
         <v>595</v>
       </c>
@@ -3810,27 +3831,25 @@
         <v>8</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="1" t="s">
-        <v>152</v>
+        <v>15</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>64</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E37" s="1"/>
       <c r="F37" s="1" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>595</v>
@@ -3839,25 +3858,23 @@
         <v>8</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>144</v>
+        <v>313</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>191</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1" t="s">
         <v>595</v>
@@ -3866,94 +3883,104 @@
         <v>8</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>253</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="1" t="s">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>68</v>
+        <v>189</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>192</v>
+        <v>64</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>595</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>500</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B40" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="C40" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E40" s="1"/>
+        <v>66</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="G41" s="1" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>196</v>
+        <v>500</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
@@ -3964,23 +3991,21 @@
         <v>8</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B43" s="1"/>
-      <c r="C43" s="2" t="s">
-        <v>274</v>
+      <c r="C43" s="5" t="s">
+        <v>303</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>209</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1" t="s">
         <v>604</v>
@@ -3989,19 +4014,19 @@
         <v>8</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="1" t="s">
-        <v>154</v>
+        <v>72</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -4012,19 +4037,24 @@
         <v>8</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="1" t="s">
-        <v>346</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B45" s="1"/>
       <c r="C45" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>334</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F45" s="1"/>
       <c r="G45" s="1" t="s">
         <v>604</v>
       </c>
@@ -4032,262 +4062,257 @@
         <v>8</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>335</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>309</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="B46" s="1"/>
       <c r="C46" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>26</v>
+        <v>275</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1" t="s">
-        <v>75</v>
+        <v>604</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
+        <v>346</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>334</v>
+      </c>
       <c r="G47" s="1" t="s">
-        <v>75</v>
+        <v>604</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>254</v>
+        <v>335</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="1" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>144</v>
+        <v>309</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>191</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
-        <v>601</v>
+        <v>75</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>253</v>
+        <v>202</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B49" s="1"/>
-      <c r="C49" s="2" t="s">
-        <v>276</v>
+        <v>25</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>315</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="E49" s="1"/>
-      <c r="F49" s="1" t="s">
-        <v>206</v>
-      </c>
+      <c r="F49" s="1"/>
       <c r="G49" s="1" t="s">
-        <v>601</v>
+        <v>75</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="1" t="s">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>80</v>
+        <v>271</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>81</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="F50" s="1"/>
       <c r="G50" s="1" t="s">
         <v>601</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>208</v>
+        <v>253</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="1" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>211</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="E51" s="1"/>
       <c r="F51" s="1" t="s">
-        <v>84</v>
+        <v>206</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>601</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>325</v>
+        <v>79</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>601</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>323</v>
+        <v>208</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>326</v>
+        <v>82</v>
+      </c>
+      <c r="B53" s="1"/>
+      <c r="C53" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>601</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>327</v>
+        <v>210</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B54" s="1"/>
-      <c r="C54" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
+        <v>324</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>325</v>
+      </c>
       <c r="G54" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>212</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B55" s="1"/>
-      <c r="C55" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
+        <v>328</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>326</v>
+      </c>
       <c r="G55" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>215</v>
+        <v>327</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="2" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>88</v>
+        <v>296</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="3" t="s">
-        <v>213</v>
-      </c>
+      <c r="F56" s="1"/>
       <c r="G56" s="1" t="s">
         <v>602</v>
       </c>
@@ -4295,19 +4320,19 @@
         <v>8</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="1" t="s">
-        <v>305</v>
+        <v>86</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
@@ -4318,22 +4343,24 @@
         <v>8</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="1" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="2" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>290</v>
+        <v>88</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
+      <c r="F58" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="G58" s="1" t="s">
         <v>602</v>
       </c>
@@ -4341,19 +4368,19 @@
         <v>8</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="1" t="s">
-        <v>89</v>
+        <v>305</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>217</v>
+        <v>294</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
@@ -4364,19 +4391,19 @@
         <v>8</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="1" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
@@ -4387,19 +4414,19 @@
         <v>8</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
@@ -4410,19 +4437,19 @@
         <v>8</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="1" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
@@ -4433,19 +4460,19 @@
         <v>8</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>299</v>
+        <v>220</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
@@ -4456,19 +4483,19 @@
         <v>8</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="1" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
@@ -4479,67 +4506,67 @@
         <v>8</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>280</v>
+        <v>92</v>
+      </c>
+      <c r="B65" s="1"/>
+      <c r="C65" s="2" t="s">
+        <v>262</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="1" t="s">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B67" s="1"/>
-      <c r="C67" s="2" t="s">
-        <v>262</v>
+        <v>102</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>280</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>95</v>
+        <v>292</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
@@ -4550,19 +4577,19 @@
         <v>8</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="1" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
@@ -4573,19 +4600,19 @@
         <v>8</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>302</v>
+        <v>95</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
@@ -4596,19 +4623,19 @@
         <v>8</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>99</v>
+        <v>301</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
@@ -4619,19 +4646,19 @@
         <v>8</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B71" s="1"/>
       <c r="C71" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>101</v>
+        <v>302</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
@@ -4642,19 +4669,19 @@
         <v>8</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>220</v>
+        <v>99</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
@@ -4665,19 +4692,19 @@
         <v>8</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="1" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>298</v>
+        <v>101</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -4688,80 +4715,74 @@
         <v>8</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>311</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="B74" s="1"/>
       <c r="C74" s="2" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>11</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
       <c r="G74" s="1" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>146</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B75" s="1"/>
       <c r="C75" s="2" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>232</v>
+        <v>298</v>
       </c>
       <c r="E75" s="1"/>
-      <c r="F75" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="F75" s="1"/>
       <c r="G75" s="1" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="1" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>147</v>
+        <v>311</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
+        <v>281</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="G76" s="1" t="s">
         <v>596</v>
       </c>
@@ -4769,24 +4790,26 @@
         <v>8</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="1" t="s">
-        <v>306</v>
+        <v>103</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>308</v>
+        <v>282</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
+      <c r="F77" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="G77" s="1" t="s">
         <v>596</v>
       </c>
@@ -4794,25 +4817,23 @@
         <v>8</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>284</v>
+        <v>147</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>283</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>239</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1" t="s">
         <v>596</v>
@@ -4821,21 +4842,21 @@
         <v>8</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="1" t="s">
-        <v>107</v>
+        <v>306</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>241</v>
+        <v>308</v>
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
@@ -4846,23 +4867,25 @@
         <v>8</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>286</v>
+        <v>237</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>284</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E80" s="1"/>
+        <v>238</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="F80" s="1"/>
       <c r="G80" s="1" t="s">
         <v>596</v>
@@ -4871,85 +4894,77 @@
         <v>8</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="1" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>255</v>
+        <v>149</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>69</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
       <c r="G81" s="1" t="s">
         <v>596</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>501</v>
+        <v>242</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>112</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
       <c r="G82" s="1" t="s">
         <v>596</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="1" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>287</v>
+      <c r="C83" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>245</v>
+        <v>68</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>246</v>
+        <v>192</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>596</v>
@@ -4958,84 +4973,84 @@
         <v>24</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>247</v>
+        <v>501</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="1" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>66</v>
+        <v>257</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F84" s="1"/>
+        <v>110</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="G84" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>311</v>
+        <v>136</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>10</v>
+        <v>287</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>203</v>
+        <v>246</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="F86" s="1"/>
       <c r="G86" s="1" t="s">
         <v>597</v>
       </c>
@@ -5043,25 +5058,27 @@
         <v>8</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E87" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="F87" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>597</v>
@@ -5070,24 +5087,28 @@
         <v>8</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>313</v>
+        <v>141</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="G88" s="1" t="s">
         <v>597</v>
       </c>
@@ -5095,22 +5116,26 @@
         <v>8</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B89" s="1"/>
-      <c r="C89" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>322</v>
       </c>
       <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
+      <c r="F89" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="G89" s="1" t="s">
         <v>597</v>
       </c>
@@ -5118,19 +5143,21 @@
         <v>8</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>222</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B90" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="C90" s="2" t="s">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>21</v>
+        <v>291</v>
       </c>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
@@ -5141,50 +5168,42 @@
         <v>8</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>223</v>
+        <v>188</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>136</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B91" s="1"/>
       <c r="C91" s="2" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
       <c r="G91" s="1" t="s">
         <v>597</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>314</v>
+        <v>20</v>
+      </c>
+      <c r="B92" s="1"/>
+      <c r="C92" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
@@ -5195,24 +5214,28 @@
         <v>8</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>254</v>
+        <v>223</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="1" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
+        <v>136</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="G93" s="1" t="s">
         <v>597</v>
       </c>
@@ -5220,71 +5243,69 @@
         <v>24</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>202</v>
+        <v>247</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B94" s="1"/>
-      <c r="C94" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>198</v>
+        <v>25</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>197</v>
+        <v>254</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="1" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>248</v>
+        <v>309</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="E95" s="1"/>
-      <c r="F95" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="F95" s="1"/>
       <c r="G95" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>249</v>
+        <v>202</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>309</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="B96" s="1"/>
       <c r="C96" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>26</v>
+        <v>273</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
@@ -5292,119 +5313,137 @@
         <v>598</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B97" s="1"/>
+        <v>153</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>250</v>
+      </c>
       <c r="C97" s="2" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>74</v>
+        <v>248</v>
       </c>
       <c r="E97" s="1"/>
-      <c r="F97" s="1"/>
+      <c r="F97" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="G97" s="1" t="s">
         <v>598</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>201</v>
+        <v>249</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="1" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>151</v>
+        <v>309</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>114</v>
+        <v>310</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="E98" s="1"/>
-      <c r="F98" s="1" t="s">
-        <v>113</v>
-      </c>
+      <c r="F98" s="1"/>
       <c r="G98" s="1" t="s">
         <v>598</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B99" s="1"/>
+      <c r="C99" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="2" t="s">
         <v>561</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9">
-      <c r="A99" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9">
-      <c r="A100" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="2" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>592</v>
@@ -5413,15 +5452,15 @@
         <v>8</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>592</v>
@@ -5430,53 +5469,41 @@
         <v>8</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I104" s="13" t="s">
-        <v>374</v>
+      <c r="I104" s="1" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I105" s="13" t="s">
-        <v>374</v>
+      <c r="I105" s="1" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -5492,8 +5519,8 @@
       <c r="E106" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="G106" s="1" t="s">
-        <v>602</v>
+      <c r="G106" s="2" t="s">
+        <v>601</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>8</v>
@@ -5515,8 +5542,8 @@
       <c r="E107" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="G107" s="1" t="s">
-        <v>603</v>
+      <c r="G107" s="2" t="s">
+        <v>604</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>8</v>
@@ -5539,7 +5566,7 @@
         <v>378</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>8</v>
@@ -5550,172 +5577,160 @@
     </row>
     <row r="109" spans="1:9">
       <c r="A109" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>372</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>378</v>
       </c>
       <c r="G109" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I109" s="13" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="G110" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="H109" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9">
-      <c r="A110" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>382</v>
+      <c r="H110" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I110" s="13" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="D111" s="2" t="s">
+      <c r="D113" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="E111" s="2" t="s">
+      <c r="E113" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="G111" s="1" t="s">
+      <c r="G113" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="H111" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I111" s="1" t="s">
+      <c r="H113" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I113" s="1" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
-      <c r="A112" s="2" t="s">
+    <row r="114" spans="1:9">
+      <c r="A114" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B114" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C112" s="5" t="s">
+      <c r="C114" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="D114" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="E112" s="2" t="s">
+      <c r="E114" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="F112" s="5" t="s">
+      <c r="F114" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="G112" s="2" t="s">
+      <c r="G114" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="H112" s="2" t="s">
+      <c r="H114" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I112" s="15" t="s">
+      <c r="I114" s="15" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="23.45" customHeight="1">
-      <c r="A113" s="12" t="s">
+    <row r="115" spans="1:9" ht="23.4" customHeight="1">
+      <c r="A115" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B113" s="12" t="s">
+      <c r="B115" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="C113" s="12" t="s">
+      <c r="C115" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="D113" s="12" t="s">
+      <c r="D115" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="E113" s="6" t="s">
+      <c r="E115" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="F113" s="2" t="s">
+      <c r="F115" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="G113" s="12" t="s">
-        <v>599</v>
-      </c>
-      <c r="H113" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="I113" s="12" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9">
-      <c r="A114" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="B114" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="D114" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="E114" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="G114" s="12" t="s">
-        <v>599</v>
-      </c>
-      <c r="H114" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I114" s="12" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9">
-      <c r="A115" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="B115" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="D115" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="E115" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="G115" s="12" t="s">
         <v>599</v>
@@ -5724,212 +5739,227 @@
         <v>8</v>
       </c>
       <c r="I115" s="12" t="s">
-        <v>561</v>
+        <v>397</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="12" t="s">
-        <v>408</v>
-      </c>
-      <c r="B116" s="5"/>
-      <c r="C116" s="12"/>
+        <v>398</v>
+      </c>
+      <c r="B116" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>400</v>
+      </c>
       <c r="D116" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="E116" s="12"/>
-      <c r="F116" s="12"/>
-      <c r="G116" s="1" t="s">
-        <v>593</v>
+        <v>248</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="G116" s="12" t="s">
+        <v>599</v>
       </c>
       <c r="H116" s="12" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I116" s="12" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" s="12" t="s">
-        <v>411</v>
+        <v>155</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="E117" s="12" t="s">
-        <v>424</v>
+        <v>406</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>407</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>593</v>
+        <v>113</v>
+      </c>
+      <c r="G117" s="12" t="s">
+        <v>599</v>
       </c>
       <c r="H117" s="12" t="s">
         <v>8</v>
       </c>
       <c r="I117" s="12" t="s">
-        <v>416</v>
+        <v>561</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="B118" s="5"/>
+      <c r="C118" s="12"/>
+      <c r="D118" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="E118" s="12"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="H118" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I118" s="12" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="B119" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="E119" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="H119" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I119" s="12" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" s="12" t="s">
         <v>417</v>
       </c>
-      <c r="B118" s="12" t="s">
+      <c r="B120" s="12" t="s">
         <v>418</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C120" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D118" s="12" t="s">
+      <c r="D120" s="12" t="s">
         <v>420</v>
       </c>
-      <c r="E118" s="12" t="s">
+      <c r="E120" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="F118" s="20" t="s">
+      <c r="F120" s="20" t="s">
         <v>564</v>
       </c>
-      <c r="G118" s="12" t="s">
+      <c r="G120" s="12" t="s">
         <v>590</v>
       </c>
-      <c r="H118" s="12" t="s">
+      <c r="H120" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="I118" s="12" t="s">
+      <c r="I120" s="12" t="s">
         <v>421</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9">
-      <c r="A119" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I119" s="1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9">
-      <c r="A120" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I120" s="1" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C122" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="D122" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="E121" s="2" t="s">
+      <c r="E122" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="G121" s="1" t="s">
+      <c r="G122" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="G123" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="H121" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I121" s="1" t="s">
+      <c r="H123" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I123" s="1" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
-      <c r="A122" s="13" t="s">
+    <row r="124" spans="1:9">
+      <c r="A124" s="13" t="s">
         <v>435</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B124" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="D122" s="13" t="s">
+      <c r="D124" s="13" t="s">
         <v>437</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I122" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9">
-      <c r="A123" s="13" t="s">
-        <v>439</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D123" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="F123" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9">
-      <c r="A124" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="B124" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>596</v>
@@ -5938,24 +5968,21 @@
         <v>8</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
     </row>
     <row r="125" spans="1:9">
-      <c r="A125" s="2" t="s">
-        <v>473</v>
+      <c r="A125" s="13" t="s">
+        <v>439</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="F125" s="16" t="s">
-        <v>451</v>
+        <v>441</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>442</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>596</v>
@@ -5963,25 +5990,19 @@
       <c r="H125" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="I125" s="1" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="126" spans="1:9">
-      <c r="A126" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="D126" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="E126" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="F126" s="7" t="s">
-        <v>455</v>
+      <c r="A126" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B126" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>446</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>596</v>
@@ -5990,151 +6011,148 @@
         <v>8</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="127" spans="1:9">
-      <c r="A127" s="7" t="s">
-        <v>490</v>
-      </c>
-      <c r="B127" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>459</v>
+      <c r="A127" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>449</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="E127" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="F127" s="8"/>
+        <v>450</v>
+      </c>
+      <c r="F127" s="16" t="s">
+        <v>451</v>
+      </c>
       <c r="G127" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I127" s="17" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>463</v>
+        <v>452</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>453</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>465</v>
-      </c>
-      <c r="E128" s="7"/>
-      <c r="F128" s="13" t="s">
-        <v>466</v>
+        <v>455</v>
+      </c>
+      <c r="E128" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>455</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
     </row>
     <row r="129" spans="1:9">
-      <c r="A129" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="D129" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="E129" s="7"/>
+      <c r="A129" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="E129" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="F129" s="8"/>
       <c r="G129" s="1" t="s">
         <v>593</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I129" s="1" t="s">
-        <v>472</v>
+      <c r="I129" s="17" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="130" spans="1:9">
-      <c r="A130" s="2" t="s">
-        <v>478</v>
+      <c r="A130" s="7" t="s">
+        <v>462</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="F130" s="5" t="s">
-        <v>46</v>
+        <v>463</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="D130" s="13" t="s">
+        <v>465</v>
+      </c>
+      <c r="E130" s="7"/>
+      <c r="F130" s="13" t="s">
+        <v>466</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>593</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I130" s="17" t="s">
-        <v>479</v>
+        <v>8</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" s="2" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>483</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="E131" s="7"/>
       <c r="G131" s="1" t="s">
         <v>593</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I131" s="2" t="s">
-        <v>486</v>
+        <v>8</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="132" spans="1:9">
-      <c r="A132" s="9" t="s">
-        <v>484</v>
+      <c r="A132" s="2" t="s">
+        <v>478</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>481</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>488</v>
@@ -6142,195 +6160,196 @@
       <c r="F132" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G132" s="2" t="s">
+      <c r="G132" s="1" t="s">
         <v>593</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I132" s="2" t="s">
-        <v>485</v>
+      <c r="I132" s="17" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="133" spans="1:9">
-      <c r="A133" s="10" t="s">
-        <v>495</v>
+      <c r="A133" s="2" t="s">
+        <v>480</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>493</v>
+        <v>481</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>257</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>592</v>
+        <v>482</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>593</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="134" spans="1:9">
-      <c r="A134" s="18" t="s">
-        <v>499</v>
+      <c r="A134" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>481</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>497</v>
+        <v>487</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>24</v>
       </c>
       <c r="I134" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136" s="18" t="s">
+        <v>499</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I136" s="2" t="s">
         <v>496</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9">
-      <c r="A135" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="C135" s="11" t="s">
-        <v>511</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="G135" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I135" s="1" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9">
-      <c r="A136" s="13" t="s">
-        <v>506</v>
-      </c>
-      <c r="B136" s="13" t="s">
-        <v>507</v>
-      </c>
-      <c r="C136" s="11" t="s">
-        <v>512</v>
-      </c>
-      <c r="D136" s="11" t="s">
-        <v>508</v>
-      </c>
-      <c r="E136" s="13" t="s">
-        <v>509</v>
-      </c>
-      <c r="F136" s="13"/>
-      <c r="G136" s="13" t="s">
-        <v>601</v>
-      </c>
-      <c r="H136" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I136" s="13" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C137" s="11" t="s">
+        <v>511</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" s="13" t="s">
+        <v>506</v>
+      </c>
+      <c r="B138" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="C138" s="11" t="s">
+        <v>512</v>
+      </c>
+      <c r="D138" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="E138" s="13" t="s">
+        <v>509</v>
+      </c>
+      <c r="F138" s="13"/>
+      <c r="G138" s="13" t="s">
+        <v>601</v>
+      </c>
+      <c r="H138" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="I138" s="13" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="D137" s="2" t="s">
+      <c r="D139" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="G137" s="2" t="s">
+      <c r="G139" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="H137" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I137" s="2" t="s">
+      <c r="H139" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I139" s="2" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
-      <c r="A138" s="2" t="s">
+    <row r="140" spans="1:9">
+      <c r="A140" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D138" s="11" t="s">
+      <c r="D140" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="G138" s="2" t="s">
+      <c r="G140" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="H138" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I138" s="1" t="s">
+      <c r="H140" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I140" s="1" t="s">
         <v>520</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9">
-      <c r="A139" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="B139" s="1"/>
-      <c r="C139" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="F139" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="H139" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I139" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9">
-      <c r="A140" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="B140" s="1"/>
-      <c r="C140" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="F140" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="H140" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I140" s="1" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -6351,7 +6370,7 @@
         <v>474</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="H141" s="1" t="s">
         <v>8</v>
@@ -6378,7 +6397,7 @@
         <v>474</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>8</v>
@@ -6405,7 +6424,7 @@
         <v>474</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="H143" s="1" t="s">
         <v>8</v>
@@ -6415,72 +6434,74 @@
       </c>
     </row>
     <row r="144" spans="1:9">
-      <c r="A144" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="D144" s="11" t="s">
-        <v>562</v>
-      </c>
-      <c r="G144" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="H144" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I144" t="s">
-        <v>524</v>
+      <c r="A144" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B144" s="1"/>
+      <c r="C144" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="145" spans="1:9">
-      <c r="A145" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="B145" s="19" t="s">
-        <v>530</v>
-      </c>
-      <c r="C145" s="11" t="s">
-        <v>554</v>
-      </c>
-      <c r="D145" s="11" t="s">
-        <v>531</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="G145" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H145" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I145" t="s">
-        <v>533</v>
+      <c r="A145" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B145" s="1"/>
+      <c r="C145" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="146" spans="1:9">
       <c r="A146" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="B146" s="19" t="s">
-        <v>530</v>
-      </c>
-      <c r="C146" s="11" t="s">
-        <v>554</v>
+        <v>523</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>531</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>532</v>
+        <v>562</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -6500,7 +6521,7 @@
         <v>532</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>600</v>
+        <v>75</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>8</v>
@@ -6525,8 +6546,8 @@
       <c r="E148" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="G148" s="1" t="s">
-        <v>596</v>
+      <c r="G148" s="2" t="s">
+        <v>593</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>8</v>
@@ -6551,8 +6572,8 @@
       <c r="E149" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="G149" s="1" t="s">
-        <v>601</v>
+      <c r="G149" s="2" t="s">
+        <v>600</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>8</v>
@@ -6563,129 +6584,126 @@
     </row>
     <row r="150" spans="1:9">
       <c r="A150" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>534</v>
+        <v>563</v>
+      </c>
+      <c r="B150" s="19" t="s">
+        <v>530</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F150" s="11" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I150" s="1" t="s">
-        <v>538</v>
+        <v>8</v>
+      </c>
+      <c r="I150" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="151" spans="1:9">
       <c r="A151" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>539</v>
+        <v>563</v>
+      </c>
+      <c r="B151" s="19" t="s">
+        <v>530</v>
+      </c>
+      <c r="C151" s="11" t="s">
+        <v>554</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>598</v>
+        <v>532</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>601</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I151" s="1" t="s">
-        <v>541</v>
+      <c r="I151" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="152" spans="1:9">
       <c r="A152" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>545</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>590</v>
+        <v>537</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>598</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>24</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="153" spans="1:9">
       <c r="A153" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="C153" s="11" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>548</v>
+        <v>344</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
     </row>
     <row r="154" spans="1:9">
       <c r="A154" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="F154" s="11" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>590</v>
@@ -6694,229 +6712,242 @@
         <v>24</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
     </row>
     <row r="155" spans="1:9">
-      <c r="A155" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="B155" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="D155" s="12" t="s">
-        <v>420</v>
-      </c>
-      <c r="E155" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="F155" s="20" t="s">
-        <v>564</v>
+      <c r="A155" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C155" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="D155" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>548</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="H155" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I155" s="12" t="s">
-        <v>421</v>
+        <v>604</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="156" spans="1:9">
       <c r="A156" s="2" t="s">
-        <v>502</v>
+        <v>529</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>560</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>511</v>
-      </c>
-      <c r="D156" s="20" t="s">
-        <v>503</v>
-      </c>
-      <c r="F156" s="2" t="s">
-        <v>504</v>
+        <v>558</v>
+      </c>
+      <c r="D156" s="11" t="s">
+        <v>550</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="F156" s="11" t="s">
+        <v>552</v>
       </c>
       <c r="G156" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="A157" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="B157" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D157" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="E157" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="F157" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="G157" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="H156" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I156" s="1" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9">
-      <c r="A157" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="B157" s="21"/>
-      <c r="D157" s="20" t="s">
-        <v>566</v>
-      </c>
-      <c r="E157" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="G157" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="H157" s="2" t="s">
+      <c r="H157" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="I157" s="1" t="s">
-        <v>565</v>
+      <c r="I157" s="12" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:9">
       <c r="A158" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="B158" s="21"/>
-      <c r="C158" s="20" t="s">
-        <v>573</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="E158" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C158" s="11" t="s">
+        <v>511</v>
+      </c>
+      <c r="D158" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="A159" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B159" s="21"/>
+      <c r="D159" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="E159" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="G158" s="2" t="s">
+      <c r="G159" s="2" t="s">
         <v>596</v>
-      </c>
-      <c r="H158" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I158" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9">
-      <c r="A159" s="13" t="s">
-        <v>571</v>
-      </c>
-      <c r="B159" t="s">
-        <v>576</v>
-      </c>
-      <c r="C159" s="20" t="s">
-        <v>574</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="F159" s="20" t="s">
-        <v>575</v>
-      </c>
-      <c r="G159" s="2" t="s">
-        <v>590</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>24</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
     </row>
     <row r="160" spans="1:9">
-      <c r="A160" s="13" t="s">
-        <v>577</v>
-      </c>
-      <c r="C160" t="s">
-        <v>587</v>
-      </c>
-      <c r="D160" s="20" t="s">
-        <v>578</v>
-      </c>
-      <c r="F160" s="20" t="s">
-        <v>586</v>
+      <c r="A160" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B160" s="21"/>
+      <c r="C160" s="20" t="s">
+        <v>573</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>596</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I160" s="1" t="s">
-        <v>580</v>
+        <v>8</v>
+      </c>
+      <c r="I160" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="161" spans="1:9">
-      <c r="A161" s="2" t="s">
-        <v>581</v>
+      <c r="A161" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="B161" t="s">
+        <v>576</v>
+      </c>
+      <c r="C161" s="20" t="s">
+        <v>574</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>572</v>
       </c>
+      <c r="F161" s="20" t="s">
+        <v>575</v>
+      </c>
       <c r="G161" s="2" t="s">
         <v>590</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I161" t="s">
-        <v>582</v>
+      <c r="I161" s="1" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="162" spans="1:9">
-      <c r="A162" s="2" t="s">
-        <v>584</v>
+      <c r="A162" s="13" t="s">
+        <v>577</v>
+      </c>
+      <c r="C162" t="s">
+        <v>587</v>
       </c>
       <c r="D162" s="20" t="s">
-        <v>583</v>
+        <v>578</v>
+      </c>
+      <c r="F162" s="20" t="s">
+        <v>586</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="B163" s="21"/>
-      <c r="D163" s="20" t="s">
-        <v>566</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>344</v>
+        <v>581</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>572</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I163" s="1" t="s">
-        <v>565</v>
+      <c r="I163" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="164" spans="1:9">
       <c r="A164" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="B164" s="21"/>
+        <v>584</v>
+      </c>
       <c r="D164" s="20" t="s">
-        <v>566</v>
-      </c>
-      <c r="E164" s="2" t="s">
-        <v>344</v>
+        <v>583</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>565</v>
+        <v>585</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -6924,7 +6955,6 @@
         <v>567</v>
       </c>
       <c r="B165" s="21"/>
-      <c r="C165" s="20"/>
       <c r="D165" s="20" t="s">
         <v>566</v>
       </c>
@@ -6932,7 +6962,7 @@
         <v>344</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>24</v>
@@ -6943,50 +6973,45 @@
     </row>
     <row r="166" spans="1:9">
       <c r="A166" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B166" s="21"/>
-      <c r="C166" s="20" t="s">
-        <v>588</v>
-      </c>
       <c r="D166" s="20" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>344</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I166" t="s">
-        <v>569</v>
+        <v>24</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="167" spans="1:9">
       <c r="A167" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B167" s="21"/>
-      <c r="C167" s="20" t="s">
-        <v>588</v>
-      </c>
+      <c r="C167" s="20"/>
       <c r="D167" s="20" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>344</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I167" t="s">
-        <v>569</v>
+        <v>24</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -7004,7 +7029,7 @@
         <v>344</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>8</v>
@@ -7028,7 +7053,7 @@
         <v>344</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>8</v>
@@ -7037,140 +7062,192 @@
         <v>569</v>
       </c>
     </row>
+    <row r="170" spans="1:9">
+      <c r="A170" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B170" s="21"/>
+      <c r="C170" s="20" t="s">
+        <v>588</v>
+      </c>
+      <c r="D170" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I170" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
+      <c r="A171" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B171" s="21"/>
+      <c r="C171" s="20" t="s">
+        <v>588</v>
+      </c>
+      <c r="D171" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I171" t="s">
+        <v>569</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I98">
-    <sortCondition ref="G2:G98"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:I100">
+    <sortCondition ref="G4:G100"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="F23" r:id="rId1" xr:uid="{56461029-F272-40B0-AA7C-85F66C5CF6EB}"/>
-    <hyperlink ref="F56" r:id="rId2" xr:uid="{94D7D8F8-44B5-447E-9A32-9F64E5CCF3FA}"/>
-    <hyperlink ref="C78" r:id="rId3" xr:uid="{777A5BAE-8D61-4AA7-9259-E54BD1FDBE70}"/>
-    <hyperlink ref="C81" r:id="rId4" xr:uid="{FD026EBB-4302-4206-B780-7E1F91763261}"/>
-    <hyperlink ref="C65" r:id="rId5" xr:uid="{8966019B-4C3B-4F02-A071-5411CA74F3F8}"/>
-    <hyperlink ref="D82" r:id="rId6" xr:uid="{F64C67D3-CAF8-47D7-9BBD-60BA8702A9B2}"/>
-    <hyperlink ref="D2" r:id="rId7" xr:uid="{5E75608C-EF4E-4E89-BFD2-9C98C2096B20}"/>
-    <hyperlink ref="D4" r:id="rId8" xr:uid="{5E90B8DC-AD77-4B67-993E-32CF4C9CFD26}"/>
-    <hyperlink ref="D46" r:id="rId9" xr:uid="{097C0E3E-0A06-4C08-8729-6EE0824D62F8}"/>
-    <hyperlink ref="D96" r:id="rId10" xr:uid="{6FC1A61E-CA39-4E3B-A451-51C002A830C8}"/>
-    <hyperlink ref="D93" r:id="rId11" xr:uid="{AF63B350-6BD5-4890-B968-9E23CBF2D9C4}"/>
-    <hyperlink ref="D85" r:id="rId12" xr:uid="{68410040-0123-49F9-AD96-D8FBAF000148}"/>
-    <hyperlink ref="D49" r:id="rId13" location="programs " xr:uid="{9E90FFD4-3789-45CA-8EE0-D02F471C3648}"/>
-    <hyperlink ref="D50" r:id="rId14" xr:uid="{5DADD7F9-891C-4DA9-8630-2E4F57BA4BB0}"/>
-    <hyperlink ref="D74" r:id="rId15" xr:uid="{E7FCC05F-E0C4-4B4B-9BF6-3D5388C2BBD3}"/>
-    <hyperlink ref="D58" r:id="rId16" xr:uid="{BA7221EF-B2F7-48AC-BA37-4D01E6B77745}"/>
-    <hyperlink ref="D23" r:id="rId17" xr:uid="{94B72A5A-DA9F-4A49-B6D6-869D1EB3A773}"/>
-    <hyperlink ref="D57" r:id="rId18" xr:uid="{D1114FE8-20D3-4F80-B444-5686CFBB7223}"/>
-    <hyperlink ref="D56" r:id="rId19" xr:uid="{4A5896AC-FF3D-4F52-9EEA-57FA7C298A0F}"/>
-    <hyperlink ref="D55" r:id="rId20" xr:uid="{EB5F5F74-D4A1-4286-B2C3-3B240C8A0B3A}"/>
-    <hyperlink ref="D54" r:id="rId21" xr:uid="{A4E9F103-D8DF-4A08-B73B-82C9402281E0}"/>
-    <hyperlink ref="D51" r:id="rId22" xr:uid="{7C9B8008-6FC3-4D8B-9FAC-859864B3CCA6}"/>
-    <hyperlink ref="D59" r:id="rId23" xr:uid="{8B92366E-1104-40D7-B41A-5F9D960F675C}"/>
-    <hyperlink ref="D60" r:id="rId24" xr:uid="{BA61B788-1EE1-4D0A-BE68-5496335960B2}"/>
-    <hyperlink ref="D61" r:id="rId25" xr:uid="{788ED0D2-F799-42C7-BE70-26DAA5615100}"/>
-    <hyperlink ref="D62" r:id="rId26" xr:uid="{5315C9E9-D76A-423C-BFE1-AF451A0BCC1E}"/>
-    <hyperlink ref="D63" r:id="rId27" xr:uid="{BC82856E-908A-45D9-A41B-408B8FC5E720}"/>
-    <hyperlink ref="D64" r:id="rId28" xr:uid="{BFEA5820-6FEF-4AB5-AFDC-035AB404A7DA}"/>
-    <hyperlink ref="D65" r:id="rId29" xr:uid="{76669F61-A905-4387-B0E8-34E4D1366C7B}"/>
-    <hyperlink ref="D66" r:id="rId30" xr:uid="{74F9C236-EE46-491C-BF5A-2DFA889F7A26}"/>
-    <hyperlink ref="D67" r:id="rId31" xr:uid="{C8AC3248-2D61-4C9F-9CC4-96E24312EBEA}"/>
-    <hyperlink ref="D68" r:id="rId32" xr:uid="{B26C8AAE-4B11-4F8E-B74E-F7458BF05D09}"/>
-    <hyperlink ref="D69" r:id="rId33" xr:uid="{2A1A49A2-F37D-4774-AE8D-F594F26111D7}"/>
-    <hyperlink ref="D70" r:id="rId34" xr:uid="{9B7A9104-CDE8-4FC8-A2F3-845B8C3DB23E}"/>
-    <hyperlink ref="D71" r:id="rId35" xr:uid="{CF5BDF24-B56F-4FFF-B0DB-92F7D035BE83}"/>
-    <hyperlink ref="D72" r:id="rId36" xr:uid="{42118767-4820-49B5-A394-949C14367612}"/>
-    <hyperlink ref="D73" r:id="rId37" xr:uid="{B2C0A57F-0293-4754-8D4A-7C784AF7C213}"/>
-    <hyperlink ref="D75" r:id="rId38" xr:uid="{D07F3365-A219-44A8-BDED-0A41BC7D7571}"/>
-    <hyperlink ref="D41" r:id="rId39" xr:uid="{019C03B9-1170-401E-B03B-C29FC6CF108A}"/>
-    <hyperlink ref="C41" r:id="rId40" xr:uid="{33BA4AA8-12EB-4D42-B2D2-FB4088026AE5}"/>
-    <hyperlink ref="C16" r:id="rId41" xr:uid="{05C5E1C3-5F61-4D07-9629-20A9D90C9635}"/>
-    <hyperlink ref="C93" r:id="rId42" xr:uid="{FDB1E1E6-ADD8-4564-8753-565B078034C8}"/>
-    <hyperlink ref="D87" r:id="rId43" xr:uid="{D469BF19-F67A-4157-A0FF-1AA4B9E0BF23}"/>
-    <hyperlink ref="D35" r:id="rId44" xr:uid="{D2E0A897-D81C-4125-9C47-3A8C879089DB}"/>
-    <hyperlink ref="C35" r:id="rId45" xr:uid="{B62AA879-0896-4DFB-BBCE-B7490B146B3E}"/>
-    <hyperlink ref="C87" r:id="rId46" xr:uid="{9F59640A-1CEF-4A8B-B161-21254F4837CD}"/>
-    <hyperlink ref="D92" r:id="rId47" xr:uid="{863F960F-332F-4E54-B6FE-24604DF43AE0}"/>
-    <hyperlink ref="D47" r:id="rId48" xr:uid="{1625DFE4-6C48-4A82-8811-F4EEB64C2D2F}"/>
-    <hyperlink ref="C47" r:id="rId49" xr:uid="{7C99B3A7-0A0D-4CE1-93C6-1839F51BF301}"/>
-    <hyperlink ref="C92" r:id="rId50" xr:uid="{450BC70E-87BA-43CB-B09E-27FB7290B23E}"/>
-    <hyperlink ref="D52" r:id="rId51" xr:uid="{968FB6ED-3EE3-4000-9ED4-DED4170844E0}"/>
-    <hyperlink ref="D53" r:id="rId52" xr:uid="{F95FFAFA-D649-4148-ACBF-893459976BA3}"/>
-    <hyperlink ref="D28" r:id="rId53" xr:uid="{867A5CA1-DED0-4BC8-AA9D-0AC38C76154A}"/>
-    <hyperlink ref="C28" r:id="rId54" xr:uid="{33C23722-2292-452E-A86A-F2FF5F22AC03}"/>
-    <hyperlink ref="C17" r:id="rId55" xr:uid="{F89D664A-980E-4238-B48D-9E9A504E1383}"/>
-    <hyperlink ref="C104" r:id="rId56" xr:uid="{51C929CE-DB05-4DB6-84D8-85DAEC31CA86}"/>
-    <hyperlink ref="C105" r:id="rId57" xr:uid="{9F47A25C-362F-482B-B273-28CEF5F32C42}"/>
-    <hyperlink ref="C106" r:id="rId58" xr:uid="{64711161-99CC-43DD-9210-5E37A90E2DC5}"/>
-    <hyperlink ref="C107" r:id="rId59" xr:uid="{DF29EEE0-9F8D-4CF7-A923-7DC294F875C1}"/>
-    <hyperlink ref="C108" r:id="rId60" xr:uid="{81445D97-055E-4976-A30D-35BCE81CA70D}"/>
-    <hyperlink ref="D110" r:id="rId61" xr:uid="{693DB290-21F0-4514-9B8B-A8622C7B663B}"/>
-    <hyperlink ref="C112" r:id="rId62" xr:uid="{D55A67DC-BCF5-42B3-A86F-2339F8569063}"/>
-    <hyperlink ref="F112" r:id="rId63" display="mailto:career@albany.edu" xr:uid="{3D51B50C-49E6-4748-8F93-05F06C5C84BC}"/>
-    <hyperlink ref="C119" r:id="rId64" xr:uid="{FCB186DB-E4AB-43E4-9D1F-D223B2641022}"/>
-    <hyperlink ref="D123" r:id="rId65" xr:uid="{480FDF2F-7B59-4251-810C-73628BB15F67}"/>
-    <hyperlink ref="D125" r:id="rId66" xr:uid="{782AF740-7E61-4A73-AC61-FACCA8448159}"/>
-    <hyperlink ref="D129" r:id="rId67" xr:uid="{E8D15C86-B9A2-49FC-8FBA-DD6355B5091B}"/>
-    <hyperlink ref="C126" r:id="rId68" xr:uid="{604F38FE-1039-4EE3-8E74-8165B8FF8430}"/>
-    <hyperlink ref="C127" r:id="rId69" xr:uid="{F0014F07-00B7-439A-9BE1-6BAE3ECD85AC}"/>
-    <hyperlink ref="C128" r:id="rId70" xr:uid="{82004575-EEEF-4DDF-972C-9340A1AA43F5}"/>
-    <hyperlink ref="C125" r:id="rId71" xr:uid="{74182992-2721-4728-8FE1-43CF72383D38}"/>
-    <hyperlink ref="C129" r:id="rId72" xr:uid="{7EBFD176-16F3-4D24-9E15-870D3D96750B}"/>
-    <hyperlink ref="F141" r:id="rId73" xr:uid="{0F9AD5BE-0C46-4CBA-ABED-01801389D4B4}"/>
-    <hyperlink ref="C141" r:id="rId74" xr:uid="{7488EE3C-4876-41B7-AD1C-E59148EF5C60}"/>
-    <hyperlink ref="F143" r:id="rId75" xr:uid="{94D425E2-BDB7-40FE-AC8D-A0E405381B9B}"/>
-    <hyperlink ref="C143" r:id="rId76" xr:uid="{8771AA61-5955-4023-916F-EA0D148D2A7D}"/>
-    <hyperlink ref="F142" r:id="rId77" xr:uid="{6E99B26B-E909-48C3-BA3B-0EEAB27C601B}"/>
-    <hyperlink ref="C142" r:id="rId78" xr:uid="{EEB16B9A-E1D2-47F9-8980-91086F1C74C7}"/>
-    <hyperlink ref="F139" r:id="rId79" xr:uid="{68D944DA-C5C2-4839-8C79-F0953BD9134E}"/>
-    <hyperlink ref="C139" r:id="rId80" xr:uid="{E8AB3E9D-8C94-415D-AB28-D7CA4C6F6343}"/>
-    <hyperlink ref="F140" r:id="rId81" xr:uid="{F3CC3505-39D1-4EEA-8FA9-8AAB6F9BF146}"/>
-    <hyperlink ref="C140" r:id="rId82" xr:uid="{7A6FF923-3DFA-4E0B-A15D-03D091C92A64}"/>
-    <hyperlink ref="C131" r:id="rId83" xr:uid="{1FA6BB05-074A-4060-BBBF-C2C63D7C12FC}"/>
-    <hyperlink ref="F130" r:id="rId84" xr:uid="{59790EAE-256A-42B0-A297-EC57CF947976}"/>
-    <hyperlink ref="F132" r:id="rId85" xr:uid="{F171B7C9-73EF-4309-8CB2-15FCE8C2CC9E}"/>
-    <hyperlink ref="D127" r:id="rId86" xr:uid="{AE4C7754-0BC6-4329-BE3F-677BC8B998A9}"/>
-    <hyperlink ref="D136" r:id="rId87" xr:uid="{9B78D813-C58E-43B6-93FE-BA5C85BE774B}"/>
-    <hyperlink ref="C135" r:id="rId88" xr:uid="{5EA92CD5-A670-4F7D-BE25-D144C30E8390}"/>
-    <hyperlink ref="C136" r:id="rId89" xr:uid="{04A96344-FBF4-45CD-BF8A-74E2E9E7A1D4}"/>
-    <hyperlink ref="D138" r:id="rId90" xr:uid="{E6E27C26-8B3F-4E6E-A7F0-56D080F5A059}"/>
-    <hyperlink ref="D145" r:id="rId91" xr:uid="{72104B61-6124-4681-83A2-C04FE8A81422}"/>
-    <hyperlink ref="D150" r:id="rId92" xr:uid="{E34F98A6-233F-4D98-AA31-6A6F8739EE10}"/>
-    <hyperlink ref="F150" r:id="rId93" xr:uid="{F2B73996-B1DF-4B50-B7BF-4A8DAC2EBCF8}"/>
-    <hyperlink ref="D151" r:id="rId94" xr:uid="{E9C2E3C3-D837-4EED-B479-25B788589D5C}"/>
-    <hyperlink ref="F152" r:id="rId95" xr:uid="{B8E43DA3-B50D-4D55-8A39-449316C19072}"/>
-    <hyperlink ref="D152" r:id="rId96" xr:uid="{93C67D5A-182E-44E5-98F0-C26DAA38348E}"/>
-    <hyperlink ref="D153" r:id="rId97" xr:uid="{EB6504E0-5D02-48B9-AA8E-AD172B0786CC}"/>
-    <hyperlink ref="F154" r:id="rId98" xr:uid="{F6FEA5C8-2D79-4B3D-8A2D-56E7162EDEEF}"/>
-    <hyperlink ref="D154" r:id="rId99" xr:uid="{5E9ADF47-E415-42D0-96AD-AC14CEFDB46A}"/>
-    <hyperlink ref="C145" r:id="rId100" xr:uid="{8F9F1B99-EA6C-4B9C-A2F0-0A5ADEB1AAC5}"/>
-    <hyperlink ref="C146" r:id="rId101" xr:uid="{7DDADF0B-37EF-456E-A584-90A75DC8E532}"/>
-    <hyperlink ref="C147" r:id="rId102" xr:uid="{4DBCE484-8796-477B-9C75-E13EC16BE78D}"/>
-    <hyperlink ref="C148" r:id="rId103" xr:uid="{4B652928-E776-4C62-81AB-B3F682C91A9B}"/>
-    <hyperlink ref="C149" r:id="rId104" xr:uid="{263071B5-2297-41D5-BD0E-1DD5BC8884ED}"/>
-    <hyperlink ref="D146:D149" r:id="rId105" display="https://www.risse-albany.org/" xr:uid="{281154D0-8EC0-4929-9B07-64C9F15DC597}"/>
-    <hyperlink ref="C150" r:id="rId106" xr:uid="{B16923BE-F0C3-427E-9F10-6F9A519FC287}"/>
-    <hyperlink ref="C152" r:id="rId107" xr:uid="{E132F971-9DCB-4C0F-937B-6476DE4ACCAD}"/>
-    <hyperlink ref="C153" r:id="rId108" xr:uid="{A00E4B55-C978-401C-8846-DB1632284D50}"/>
-    <hyperlink ref="C154" r:id="rId109" xr:uid="{7C2DE1D7-47ED-40CF-937D-415B2488F028}"/>
-    <hyperlink ref="C156" r:id="rId110" xr:uid="{B28590EE-4458-4CAE-AE78-9975E73BC873}"/>
-    <hyperlink ref="D156" r:id="rId111" xr:uid="{1E66DBCC-AB5E-4E32-804B-D7193FA752EE}"/>
-    <hyperlink ref="F118" r:id="rId112" xr:uid="{7369515B-3200-4C5D-8DBA-683E7EA7089D}"/>
-    <hyperlink ref="F155" r:id="rId113" xr:uid="{F7A76B19-1F37-4DF5-BD65-E0CE94052793}"/>
-    <hyperlink ref="C159" r:id="rId114" display="tel:518-442-3943" xr:uid="{FF797009-0F9E-2A4A-A3A7-106BF4E6C3BA}"/>
-    <hyperlink ref="C158" r:id="rId115" xr:uid="{39AC894D-928D-1945-B205-EC44DA75AA2F}"/>
-    <hyperlink ref="F159" r:id="rId116" display="mailto:passmentor@albany.edu" xr:uid="{92FF97A4-6BFD-2047-AFAC-29DC3A1B4E54}"/>
-    <hyperlink ref="D162" r:id="rId117" xr:uid="{3DE194FC-17EE-A649-8859-317715F43009}"/>
-    <hyperlink ref="F160" r:id="rId118" display="mailto:info@cdphpcycle.org" xr:uid="{C1021047-F2A6-0D44-921E-65780A9C7407}"/>
-    <hyperlink ref="D160" r:id="rId119" xr:uid="{0F5D7C84-6C50-814B-95E8-D5E467CA24AF}"/>
-    <hyperlink ref="C166" r:id="rId120" xr:uid="{690FD66A-CACE-F148-B4D1-FC887F23F5EC}"/>
-    <hyperlink ref="C167" r:id="rId121" xr:uid="{DA09BFEF-E59D-A74C-9D84-99944ED51719}"/>
-    <hyperlink ref="C168" r:id="rId122" xr:uid="{EF917863-B783-6746-BA4E-0B21880445D2}"/>
-    <hyperlink ref="C169" r:id="rId123" xr:uid="{D678F8DB-2E76-8645-8492-668ADDB70C30}"/>
-    <hyperlink ref="D169" r:id="rId124" xr:uid="{5539CF43-9824-C040-831E-11780C081C68}"/>
-    <hyperlink ref="D168" r:id="rId125" xr:uid="{9FF172EE-8CFA-AB47-93A1-C78BEC3D269B}"/>
-    <hyperlink ref="D167" r:id="rId126" xr:uid="{19A9ABBB-6357-F847-AEED-C41F8DD723D5}"/>
-    <hyperlink ref="D166" r:id="rId127" xr:uid="{572C4F40-4005-884C-965A-3699D5D51DD3}"/>
+    <hyperlink ref="F25" r:id="rId1" xr:uid="{56461029-F272-40B0-AA7C-85F66C5CF6EB}"/>
+    <hyperlink ref="F58" r:id="rId2" xr:uid="{94D7D8F8-44B5-447E-9A32-9F64E5CCF3FA}"/>
+    <hyperlink ref="C80" r:id="rId3" xr:uid="{777A5BAE-8D61-4AA7-9259-E54BD1FDBE70}"/>
+    <hyperlink ref="C83" r:id="rId4" xr:uid="{FD026EBB-4302-4206-B780-7E1F91763261}"/>
+    <hyperlink ref="C67" r:id="rId5" xr:uid="{8966019B-4C3B-4F02-A071-5411CA74F3F8}"/>
+    <hyperlink ref="D84" r:id="rId6" xr:uid="{F64C67D3-CAF8-47D7-9BBD-60BA8702A9B2}"/>
+    <hyperlink ref="D4" r:id="rId7" xr:uid="{5E75608C-EF4E-4E89-BFD2-9C98C2096B20}"/>
+    <hyperlink ref="D6" r:id="rId8" xr:uid="{5E90B8DC-AD77-4B67-993E-32CF4C9CFD26}"/>
+    <hyperlink ref="D48" r:id="rId9" xr:uid="{097C0E3E-0A06-4C08-8729-6EE0824D62F8}"/>
+    <hyperlink ref="D98" r:id="rId10" xr:uid="{6FC1A61E-CA39-4E3B-A451-51C002A830C8}"/>
+    <hyperlink ref="D95" r:id="rId11" xr:uid="{AF63B350-6BD5-4890-B968-9E23CBF2D9C4}"/>
+    <hyperlink ref="D87" r:id="rId12" xr:uid="{68410040-0123-49F9-AD96-D8FBAF000148}"/>
+    <hyperlink ref="D51" r:id="rId13" location="programs " xr:uid="{9E90FFD4-3789-45CA-8EE0-D02F471C3648}"/>
+    <hyperlink ref="D52" r:id="rId14" xr:uid="{5DADD7F9-891C-4DA9-8630-2E4F57BA4BB0}"/>
+    <hyperlink ref="D76" r:id="rId15" xr:uid="{E7FCC05F-E0C4-4B4B-9BF6-3D5388C2BBD3}"/>
+    <hyperlink ref="D60" r:id="rId16" xr:uid="{BA7221EF-B2F7-48AC-BA37-4D01E6B77745}"/>
+    <hyperlink ref="D25" r:id="rId17" xr:uid="{94B72A5A-DA9F-4A49-B6D6-869D1EB3A773}"/>
+    <hyperlink ref="D59" r:id="rId18" xr:uid="{D1114FE8-20D3-4F80-B444-5686CFBB7223}"/>
+    <hyperlink ref="D58" r:id="rId19" xr:uid="{4A5896AC-FF3D-4F52-9EEA-57FA7C298A0F}"/>
+    <hyperlink ref="D57" r:id="rId20" xr:uid="{EB5F5F74-D4A1-4286-B2C3-3B240C8A0B3A}"/>
+    <hyperlink ref="D56" r:id="rId21" xr:uid="{A4E9F103-D8DF-4A08-B73B-82C9402281E0}"/>
+    <hyperlink ref="D53" r:id="rId22" xr:uid="{7C9B8008-6FC3-4D8B-9FAC-859864B3CCA6}"/>
+    <hyperlink ref="D61" r:id="rId23" xr:uid="{8B92366E-1104-40D7-B41A-5F9D960F675C}"/>
+    <hyperlink ref="D62" r:id="rId24" xr:uid="{BA61B788-1EE1-4D0A-BE68-5496335960B2}"/>
+    <hyperlink ref="D63" r:id="rId25" xr:uid="{788ED0D2-F799-42C7-BE70-26DAA5615100}"/>
+    <hyperlink ref="D64" r:id="rId26" xr:uid="{5315C9E9-D76A-423C-BFE1-AF451A0BCC1E}"/>
+    <hyperlink ref="D65" r:id="rId27" xr:uid="{BC82856E-908A-45D9-A41B-408B8FC5E720}"/>
+    <hyperlink ref="D66" r:id="rId28" xr:uid="{BFEA5820-6FEF-4AB5-AFDC-035AB404A7DA}"/>
+    <hyperlink ref="D67" r:id="rId29" xr:uid="{76669F61-A905-4387-B0E8-34E4D1366C7B}"/>
+    <hyperlink ref="D68" r:id="rId30" xr:uid="{74F9C236-EE46-491C-BF5A-2DFA889F7A26}"/>
+    <hyperlink ref="D69" r:id="rId31" xr:uid="{C8AC3248-2D61-4C9F-9CC4-96E24312EBEA}"/>
+    <hyperlink ref="D70" r:id="rId32" xr:uid="{B26C8AAE-4B11-4F8E-B74E-F7458BF05D09}"/>
+    <hyperlink ref="D71" r:id="rId33" xr:uid="{2A1A49A2-F37D-4774-AE8D-F594F26111D7}"/>
+    <hyperlink ref="D72" r:id="rId34" xr:uid="{9B7A9104-CDE8-4FC8-A2F3-845B8C3DB23E}"/>
+    <hyperlink ref="D73" r:id="rId35" xr:uid="{CF5BDF24-B56F-4FFF-B0DB-92F7D035BE83}"/>
+    <hyperlink ref="D74" r:id="rId36" xr:uid="{42118767-4820-49B5-A394-949C14367612}"/>
+    <hyperlink ref="D75" r:id="rId37" xr:uid="{B2C0A57F-0293-4754-8D4A-7C784AF7C213}"/>
+    <hyperlink ref="D77" r:id="rId38" xr:uid="{D07F3365-A219-44A8-BDED-0A41BC7D7571}"/>
+    <hyperlink ref="D43" r:id="rId39" xr:uid="{019C03B9-1170-401E-B03B-C29FC6CF108A}"/>
+    <hyperlink ref="C43" r:id="rId40" xr:uid="{33BA4AA8-12EB-4D42-B2D2-FB4088026AE5}"/>
+    <hyperlink ref="C18" r:id="rId41" xr:uid="{05C5E1C3-5F61-4D07-9629-20A9D90C9635}"/>
+    <hyperlink ref="C95" r:id="rId42" xr:uid="{FDB1E1E6-ADD8-4564-8753-565B078034C8}"/>
+    <hyperlink ref="D89" r:id="rId43" xr:uid="{D469BF19-F67A-4157-A0FF-1AA4B9E0BF23}"/>
+    <hyperlink ref="D37" r:id="rId44" xr:uid="{D2E0A897-D81C-4125-9C47-3A8C879089DB}"/>
+    <hyperlink ref="C37" r:id="rId45" xr:uid="{B62AA879-0896-4DFB-BBCE-B7490B146B3E}"/>
+    <hyperlink ref="C89" r:id="rId46" xr:uid="{9F59640A-1CEF-4A8B-B161-21254F4837CD}"/>
+    <hyperlink ref="D94" r:id="rId47" xr:uid="{863F960F-332F-4E54-B6FE-24604DF43AE0}"/>
+    <hyperlink ref="D49" r:id="rId48" xr:uid="{1625DFE4-6C48-4A82-8811-F4EEB64C2D2F}"/>
+    <hyperlink ref="C49" r:id="rId49" xr:uid="{7C99B3A7-0A0D-4CE1-93C6-1839F51BF301}"/>
+    <hyperlink ref="C94" r:id="rId50" xr:uid="{450BC70E-87BA-43CB-B09E-27FB7290B23E}"/>
+    <hyperlink ref="D54" r:id="rId51" xr:uid="{968FB6ED-3EE3-4000-9ED4-DED4170844E0}"/>
+    <hyperlink ref="D55" r:id="rId52" xr:uid="{F95FFAFA-D649-4148-ACBF-893459976BA3}"/>
+    <hyperlink ref="D30" r:id="rId53" xr:uid="{867A5CA1-DED0-4BC8-AA9D-0AC38C76154A}"/>
+    <hyperlink ref="C30" r:id="rId54" xr:uid="{33C23722-2292-452E-A86A-F2FF5F22AC03}"/>
+    <hyperlink ref="C19" r:id="rId55" xr:uid="{F89D664A-980E-4238-B48D-9E9A504E1383}"/>
+    <hyperlink ref="C106" r:id="rId56" xr:uid="{51C929CE-DB05-4DB6-84D8-85DAEC31CA86}"/>
+    <hyperlink ref="C107" r:id="rId57" xr:uid="{9F47A25C-362F-482B-B273-28CEF5F32C42}"/>
+    <hyperlink ref="C108" r:id="rId58" xr:uid="{64711161-99CC-43DD-9210-5E37A90E2DC5}"/>
+    <hyperlink ref="C109" r:id="rId59" xr:uid="{DF29EEE0-9F8D-4CF7-A923-7DC294F875C1}"/>
+    <hyperlink ref="C110" r:id="rId60" xr:uid="{81445D97-055E-4976-A30D-35BCE81CA70D}"/>
+    <hyperlink ref="D112" r:id="rId61" xr:uid="{693DB290-21F0-4514-9B8B-A8622C7B663B}"/>
+    <hyperlink ref="C114" r:id="rId62" xr:uid="{D55A67DC-BCF5-42B3-A86F-2339F8569063}"/>
+    <hyperlink ref="F114" r:id="rId63" display="mailto:career@albany.edu" xr:uid="{3D51B50C-49E6-4748-8F93-05F06C5C84BC}"/>
+    <hyperlink ref="C121" r:id="rId64" xr:uid="{FCB186DB-E4AB-43E4-9D1F-D223B2641022}"/>
+    <hyperlink ref="D125" r:id="rId65" xr:uid="{480FDF2F-7B59-4251-810C-73628BB15F67}"/>
+    <hyperlink ref="D127" r:id="rId66" xr:uid="{782AF740-7E61-4A73-AC61-FACCA8448159}"/>
+    <hyperlink ref="D131" r:id="rId67" xr:uid="{E8D15C86-B9A2-49FC-8FBA-DD6355B5091B}"/>
+    <hyperlink ref="C128" r:id="rId68" xr:uid="{604F38FE-1039-4EE3-8E74-8165B8FF8430}"/>
+    <hyperlink ref="C129" r:id="rId69" xr:uid="{F0014F07-00B7-439A-9BE1-6BAE3ECD85AC}"/>
+    <hyperlink ref="C130" r:id="rId70" xr:uid="{82004575-EEEF-4DDF-972C-9340A1AA43F5}"/>
+    <hyperlink ref="C127" r:id="rId71" xr:uid="{74182992-2721-4728-8FE1-43CF72383D38}"/>
+    <hyperlink ref="C131" r:id="rId72" xr:uid="{7EBFD176-16F3-4D24-9E15-870D3D96750B}"/>
+    <hyperlink ref="F143" r:id="rId73" xr:uid="{0F9AD5BE-0C46-4CBA-ABED-01801389D4B4}"/>
+    <hyperlink ref="C143" r:id="rId74" xr:uid="{7488EE3C-4876-41B7-AD1C-E59148EF5C60}"/>
+    <hyperlink ref="F145" r:id="rId75" xr:uid="{94D425E2-BDB7-40FE-AC8D-A0E405381B9B}"/>
+    <hyperlink ref="C145" r:id="rId76" xr:uid="{8771AA61-5955-4023-916F-EA0D148D2A7D}"/>
+    <hyperlink ref="F144" r:id="rId77" xr:uid="{6E99B26B-E909-48C3-BA3B-0EEAB27C601B}"/>
+    <hyperlink ref="C144" r:id="rId78" xr:uid="{EEB16B9A-E1D2-47F9-8980-91086F1C74C7}"/>
+    <hyperlink ref="F141" r:id="rId79" xr:uid="{68D944DA-C5C2-4839-8C79-F0953BD9134E}"/>
+    <hyperlink ref="C141" r:id="rId80" xr:uid="{E8AB3E9D-8C94-415D-AB28-D7CA4C6F6343}"/>
+    <hyperlink ref="F142" r:id="rId81" xr:uid="{F3CC3505-39D1-4EEA-8FA9-8AAB6F9BF146}"/>
+    <hyperlink ref="C142" r:id="rId82" xr:uid="{7A6FF923-3DFA-4E0B-A15D-03D091C92A64}"/>
+    <hyperlink ref="C133" r:id="rId83" xr:uid="{1FA6BB05-074A-4060-BBBF-C2C63D7C12FC}"/>
+    <hyperlink ref="F132" r:id="rId84" xr:uid="{59790EAE-256A-42B0-A297-EC57CF947976}"/>
+    <hyperlink ref="F134" r:id="rId85" xr:uid="{F171B7C9-73EF-4309-8CB2-15FCE8C2CC9E}"/>
+    <hyperlink ref="D129" r:id="rId86" xr:uid="{AE4C7754-0BC6-4329-BE3F-677BC8B998A9}"/>
+    <hyperlink ref="D138" r:id="rId87" xr:uid="{9B78D813-C58E-43B6-93FE-BA5C85BE774B}"/>
+    <hyperlink ref="C137" r:id="rId88" xr:uid="{5EA92CD5-A670-4F7D-BE25-D144C30E8390}"/>
+    <hyperlink ref="C138" r:id="rId89" xr:uid="{04A96344-FBF4-45CD-BF8A-74E2E9E7A1D4}"/>
+    <hyperlink ref="D140" r:id="rId90" xr:uid="{E6E27C26-8B3F-4E6E-A7F0-56D080F5A059}"/>
+    <hyperlink ref="D147" r:id="rId91" xr:uid="{72104B61-6124-4681-83A2-C04FE8A81422}"/>
+    <hyperlink ref="D152" r:id="rId92" xr:uid="{E34F98A6-233F-4D98-AA31-6A6F8739EE10}"/>
+    <hyperlink ref="F152" r:id="rId93" xr:uid="{F2B73996-B1DF-4B50-B7BF-4A8DAC2EBCF8}"/>
+    <hyperlink ref="D153" r:id="rId94" xr:uid="{E9C2E3C3-D837-4EED-B479-25B788589D5C}"/>
+    <hyperlink ref="F154" r:id="rId95" xr:uid="{B8E43DA3-B50D-4D55-8A39-449316C19072}"/>
+    <hyperlink ref="D154" r:id="rId96" xr:uid="{93C67D5A-182E-44E5-98F0-C26DAA38348E}"/>
+    <hyperlink ref="D155" r:id="rId97" xr:uid="{EB6504E0-5D02-48B9-AA8E-AD172B0786CC}"/>
+    <hyperlink ref="F156" r:id="rId98" xr:uid="{F6FEA5C8-2D79-4B3D-8A2D-56E7162EDEEF}"/>
+    <hyperlink ref="D156" r:id="rId99" xr:uid="{5E9ADF47-E415-42D0-96AD-AC14CEFDB46A}"/>
+    <hyperlink ref="C147" r:id="rId100" xr:uid="{8F9F1B99-EA6C-4B9C-A2F0-0A5ADEB1AAC5}"/>
+    <hyperlink ref="C148" r:id="rId101" xr:uid="{7DDADF0B-37EF-456E-A584-90A75DC8E532}"/>
+    <hyperlink ref="C149" r:id="rId102" xr:uid="{4DBCE484-8796-477B-9C75-E13EC16BE78D}"/>
+    <hyperlink ref="C150" r:id="rId103" xr:uid="{4B652928-E776-4C62-81AB-B3F682C91A9B}"/>
+    <hyperlink ref="C151" r:id="rId104" xr:uid="{263071B5-2297-41D5-BD0E-1DD5BC8884ED}"/>
+    <hyperlink ref="D148:D151" r:id="rId105" display="https://www.risse-albany.org/" xr:uid="{281154D0-8EC0-4929-9B07-64C9F15DC597}"/>
+    <hyperlink ref="C152" r:id="rId106" xr:uid="{B16923BE-F0C3-427E-9F10-6F9A519FC287}"/>
+    <hyperlink ref="C154" r:id="rId107" xr:uid="{E132F971-9DCB-4C0F-937B-6476DE4ACCAD}"/>
+    <hyperlink ref="C155" r:id="rId108" xr:uid="{A00E4B55-C978-401C-8846-DB1632284D50}"/>
+    <hyperlink ref="C156" r:id="rId109" xr:uid="{7C2DE1D7-47ED-40CF-937D-415B2488F028}"/>
+    <hyperlink ref="C158" r:id="rId110" xr:uid="{B28590EE-4458-4CAE-AE78-9975E73BC873}"/>
+    <hyperlink ref="D158" r:id="rId111" xr:uid="{1E66DBCC-AB5E-4E32-804B-D7193FA752EE}"/>
+    <hyperlink ref="F120" r:id="rId112" xr:uid="{7369515B-3200-4C5D-8DBA-683E7EA7089D}"/>
+    <hyperlink ref="F157" r:id="rId113" xr:uid="{F7A76B19-1F37-4DF5-BD65-E0CE94052793}"/>
+    <hyperlink ref="C161" r:id="rId114" display="tel:518-442-3943" xr:uid="{FF797009-0F9E-2A4A-A3A7-106BF4E6C3BA}"/>
+    <hyperlink ref="C160" r:id="rId115" xr:uid="{39AC894D-928D-1945-B205-EC44DA75AA2F}"/>
+    <hyperlink ref="F161" r:id="rId116" display="mailto:passmentor@albany.edu" xr:uid="{92FF97A4-6BFD-2047-AFAC-29DC3A1B4E54}"/>
+    <hyperlink ref="D164" r:id="rId117" xr:uid="{3DE194FC-17EE-A649-8859-317715F43009}"/>
+    <hyperlink ref="F162" r:id="rId118" display="mailto:info@cdphpcycle.org" xr:uid="{C1021047-F2A6-0D44-921E-65780A9C7407}"/>
+    <hyperlink ref="D162" r:id="rId119" xr:uid="{0F5D7C84-6C50-814B-95E8-D5E467CA24AF}"/>
+    <hyperlink ref="C168" r:id="rId120" xr:uid="{690FD66A-CACE-F148-B4D1-FC887F23F5EC}"/>
+    <hyperlink ref="C169" r:id="rId121" xr:uid="{DA09BFEF-E59D-A74C-9D84-99944ED51719}"/>
+    <hyperlink ref="C170" r:id="rId122" xr:uid="{EF917863-B783-6746-BA4E-0B21880445D2}"/>
+    <hyperlink ref="C171" r:id="rId123" xr:uid="{D678F8DB-2E76-8645-8492-668ADDB70C30}"/>
+    <hyperlink ref="D171" r:id="rId124" xr:uid="{5539CF43-9824-C040-831E-11780C081C68}"/>
+    <hyperlink ref="D170" r:id="rId125" xr:uid="{9FF172EE-8CFA-AB47-93A1-C78BEC3D269B}"/>
+    <hyperlink ref="D169" r:id="rId126" xr:uid="{19A9ABBB-6357-F847-AEED-C41F8DD723D5}"/>
+    <hyperlink ref="D168" r:id="rId127" xr:uid="{572C4F40-4005-884C-965A-3699D5D51DD3}"/>
+    <hyperlink ref="C3" r:id="rId128" xr:uid="{5B84A66F-FCDA-4D4A-83C8-BD05BBD34DCB}"/>
+    <hyperlink ref="D3" r:id="rId129" xr:uid="{0447BF89-BCC8-4E10-85F9-CBE7F49F4825}"/>
+    <hyperlink ref="C2" r:id="rId130" xr:uid="{BB16B2C9-ED93-4AB5-A09C-96E26E039168}"/>
+    <hyperlink ref="D2" r:id="rId131" xr:uid="{EFBC5402-9831-4D37-BDB2-F305566A4EE7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId128"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId132"/>
 </worksheet>
 </file>
--- a/data-raw/Rolodex.xlsx
+++ b/data-raw/Rolodex.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JG979646\Desktop\Rolodex\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EO276194\Desktop\Rolodex\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA11D5F1-3D87-4D28-860C-3C62EEA563EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F997E5DC-5C91-462A-A9CB-B529E40A3945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rolodex NEW" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="605">
   <si>
     <t>Name</t>
   </si>
@@ -1921,24 +1921,6 @@
   </si>
   <si>
     <t>Hotlines</t>
-  </si>
-  <si>
-    <t>Joe's Resource</t>
-  </si>
-  <si>
-    <t>1800 Penn Ave</t>
-  </si>
-  <si>
-    <t>tel:5555555555</t>
-  </si>
-  <si>
-    <t>https://google.com</t>
-  </si>
-  <si>
-    <t>M-F: 9:00 AM - 9:00 PM</t>
-  </si>
-  <si>
-    <t>A new Sexual Health Resource on campus as of June 2026</t>
   </si>
 </sst>
 </file>
@@ -2517,7 +2499,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2552,7 +2534,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="42" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2909,16 +2890,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I171"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.6"/>
+  <dimension ref="A1:I169"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="88.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="43.109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="96.33203125" style="2" customWidth="1"/>
-    <col min="5" max="8" width="25.109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="78.109375" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.6640625" style="2"/>
+    <col min="1" max="1" width="88.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="96.28515625" style="2" customWidth="1"/>
+    <col min="5" max="8" width="25.140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="78.140625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2952,76 +2933,80 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>605</v>
+        <v>118</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>607</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>608</v>
+        <v>128</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="F2" s="1"/>
+        <v>157</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="G2" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>610</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>605</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>607</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>608</v>
+        <v>137</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="F3" s="1"/>
+        <v>318</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="G3" s="1" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>610</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>119</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>590</v>
@@ -3030,27 +3015,27 @@
         <v>24</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>513</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>318</v>
+        <v>161</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>590</v>
@@ -3059,27 +3044,25 @@
         <v>24</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>159</v>
+        <v>514</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>158</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>590</v>
@@ -3088,27 +3071,25 @@
         <v>24</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>513</v>
+        <v>38</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>161</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>590</v>
@@ -3117,12 +3098,12 @@
         <v>24</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>514</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>130</v>
@@ -3131,11 +3112,11 @@
         <v>260</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>590</v>
@@ -3144,25 +3125,27 @@
         <v>24</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>164</v>
+      </c>
       <c r="F9" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>590</v>
@@ -3171,97 +3154,75 @@
         <v>24</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>251</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>130</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="B10" s="1"/>
       <c r="C10" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E10" s="1"/>
-      <c r="F10" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="1" customFormat="1">
       <c r="A11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>257</v>
+        <v>364</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="1" customFormat="1">
       <c r="A12" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="2" t="s">
-        <v>261</v>
+        <v>368</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+        <v>369</v>
+      </c>
       <c r="G12" s="1" t="s">
         <v>592</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>317</v>
+      <c r="I12" s="4" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="1" customFormat="1">
       <c r="A13" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>47</v>
+        <v>366</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>592</v>
@@ -3269,84 +3230,95 @@
       <c r="H13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="1" customFormat="1">
+      <c r="I13" s="12" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>368</v>
+        <v>48</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="2" t="s">
+        <v>316</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>369</v>
+        <v>49</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>592</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="1" customFormat="1">
+        <v>24</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>365</v>
+        <v>76</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>366</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
         <v>592</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I15" s="12" t="s">
-        <v>367</v>
+      <c r="I15" s="1" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="2" t="s">
-        <v>316</v>
+        <v>122</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>304</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
         <v>592</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
+        <v>319</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>320</v>
+      </c>
       <c r="G17" s="1" t="s">
         <v>592</v>
       </c>
@@ -3354,57 +3326,70 @@
         <v>8</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>169</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>304</v>
+        <v>130</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>264</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="G18" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>320</v>
+        <v>123</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>321</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>130</v>
@@ -3428,12 +3413,12 @@
         <v>24</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>130</v>
@@ -3457,12 +3442,12 @@
         <v>24</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>130</v>
@@ -3486,85 +3471,85 @@
         <v>24</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="1" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>52</v>
+        <v>265</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>293</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>53</v>
+        <v>177</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="1" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="1" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>293</v>
+        <v>262</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>178</v>
+        <v>57</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>593</v>
@@ -3573,27 +3558,25 @@
         <v>24</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>180</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E26" s="1"/>
       <c r="F26" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>593</v>
@@ -3602,74 +3585,61 @@
         <v>24</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>181</v>
+        <v>252</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>182</v>
+        <v>330</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>183</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>60</v>
+        <v>71</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>195</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="F28" s="1"/>
       <c r="G28" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>252</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>331</v>
+        <v>346</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>334</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>594</v>
@@ -3678,41 +3648,32 @@
         <v>8</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
+        <v>336</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>337</v>
+      </c>
       <c r="G30" s="1" t="s">
         <v>594</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I30" s="1" t="s">
-        <v>196</v>
+      <c r="I30" s="13" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>334</v>
+        <v>339</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>340</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>594</v>
@@ -3720,81 +3681,103 @@
       <c r="H31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I31" s="1" t="s">
-        <v>335</v>
+      <c r="I31" s="14" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="1" t="s">
-        <v>336</v>
+      <c r="A32" s="2" t="s">
+        <v>342</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="G32" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="H32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I32" s="13" t="s">
-        <v>338</v>
+      <c r="H32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>340</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F33" s="1"/>
       <c r="G33" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I33" s="14" t="s">
-        <v>341</v>
+      <c r="I33" s="1" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="H34" s="2" t="s">
+      <c r="A34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>345</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="1" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F35" s="1"/>
+        <v>142</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="G35" s="1" t="s">
         <v>595</v>
       </c>
@@ -3802,28 +3785,24 @@
         <v>8</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>141</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
       <c r="G36" s="1" t="s">
         <v>595</v>
       </c>
@@ -3831,25 +3810,27 @@
         <v>8</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="1" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E37" s="1"/>
+        <v>143</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="F37" s="1" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>595</v>
@@ -3858,23 +3839,25 @@
         <v>8</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>313</v>
+        <v>144</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E38" s="1"/>
+        <v>66</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1" t="s">
         <v>595</v>
@@ -3883,104 +3866,94 @@
         <v>8</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>188</v>
+        <v>253</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="1" t="s">
-        <v>152</v>
+        <v>67</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>189</v>
+        <v>68</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>64</v>
+        <v>192</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>595</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>190</v>
+        <v>500</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>144</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B40" s="1"/>
       <c r="C40" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>191</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1" t="s">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>253</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>69</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
       <c r="G41" s="1" t="s">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>500</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
@@ -3991,21 +3964,23 @@
         <v>8</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B43" s="1"/>
-      <c r="C43" s="5" t="s">
-        <v>303</v>
+      <c r="C43" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E43" s="1"/>
+        <v>199</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>209</v>
+      </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1" t="s">
         <v>604</v>
@@ -4014,19 +3989,19 @@
         <v>8</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="1" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -4037,24 +4012,19 @@
         <v>8</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B45" s="1"/>
+        <v>346</v>
+      </c>
       <c r="C45" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F45" s="1"/>
+        <v>333</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>334</v>
+      </c>
       <c r="G45" s="1" t="s">
         <v>604</v>
       </c>
@@ -4062,257 +4032,262 @@
         <v>8</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>200</v>
+        <v>335</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B46" s="1"/>
+        <v>127</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>309</v>
+      </c>
       <c r="C46" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>74</v>
+        <v>310</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1" t="s">
-        <v>604</v>
+        <v>75</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>334</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
       <c r="G47" s="1" t="s">
-        <v>604</v>
+        <v>75</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>335</v>
+        <v>254</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="1" t="s">
-        <v>127</v>
+        <v>7</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>309</v>
+        <v>144</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E48" s="1"/>
+        <v>271</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
-        <v>75</v>
+        <v>601</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>202</v>
+        <v>253</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>315</v>
+        <v>121</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="2" t="s">
+        <v>276</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>314</v>
+        <v>77</v>
       </c>
       <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
+      <c r="F49" s="1" t="s">
+        <v>206</v>
+      </c>
       <c r="G49" s="1" t="s">
-        <v>75</v>
+        <v>601</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="1" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>66</v>
+        <v>277</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F50" s="1"/>
+        <v>207</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="G50" s="1" t="s">
         <v>601</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>253</v>
+        <v>208</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="1" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E51" s="1"/>
+        <v>83</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="F51" s="1" t="s">
-        <v>206</v>
+        <v>84</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>601</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>81</v>
+        <v>324</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>325</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>601</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>208</v>
+        <v>323</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B53" s="1"/>
-      <c r="C53" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>84</v>
+        <v>328</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>326</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>601</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>210</v>
+        <v>327</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>325</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="B54" s="1"/>
+      <c r="C54" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
       <c r="G54" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>323</v>
+        <v>212</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>326</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="B55" s="1"/>
+      <c r="C55" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
       <c r="G55" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>327</v>
+        <v>215</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="2" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>296</v>
+        <v>88</v>
       </c>
       <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
+      <c r="F56" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="G56" s="1" t="s">
         <v>602</v>
       </c>
@@ -4320,19 +4295,19 @@
         <v>8</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="1" t="s">
-        <v>86</v>
+        <v>305</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
@@ -4343,24 +4318,22 @@
         <v>8</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="1" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58" s="2" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>88</v>
+        <v>290</v>
       </c>
       <c r="E58" s="1"/>
-      <c r="F58" s="3" t="s">
-        <v>213</v>
-      </c>
+      <c r="F58" s="1"/>
       <c r="G58" s="1" t="s">
         <v>602</v>
       </c>
@@ -4368,19 +4341,19 @@
         <v>8</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="1" t="s">
-        <v>305</v>
+        <v>89</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>294</v>
+        <v>217</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
@@ -4391,19 +4364,19 @@
         <v>8</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="1" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
@@ -4414,19 +4387,19 @@
         <v>8</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
@@ -4437,19 +4410,19 @@
         <v>8</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="1" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
@@ -4460,19 +4433,19 @@
         <v>8</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>220</v>
+        <v>299</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
@@ -4483,19 +4456,19 @@
         <v>8</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="1" t="s">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
@@ -4506,67 +4479,67 @@
         <v>8</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B65" s="1"/>
-      <c r="C65" s="2" t="s">
-        <v>262</v>
+        <v>102</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>280</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="1" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>280</v>
+        <v>94</v>
+      </c>
+      <c r="B67" s="1"/>
+      <c r="C67" s="2" t="s">
+        <v>262</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>292</v>
+        <v>95</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
@@ -4577,19 +4550,19 @@
         <v>8</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
@@ -4600,19 +4573,19 @@
         <v>8</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>95</v>
+        <v>302</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
@@ -4623,19 +4596,19 @@
         <v>8</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>301</v>
+        <v>99</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
@@ -4646,19 +4619,19 @@
         <v>8</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B71" s="1"/>
       <c r="C71" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>302</v>
+        <v>101</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
@@ -4669,19 +4642,19 @@
         <v>8</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="1" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B72" s="1"/>
       <c r="C72" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
@@ -4692,19 +4665,19 @@
         <v>8</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="1" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>101</v>
+        <v>298</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -4715,74 +4688,80 @@
         <v>8</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B74" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>311</v>
+      </c>
       <c r="C74" s="2" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="G74" s="1" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B75" s="1"/>
+        <v>103</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="C75" s="2" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>298</v>
+        <v>232</v>
       </c>
       <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
+      <c r="F75" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="G75" s="1" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="1" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>311</v>
+        <v>147</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>11</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
       <c r="G76" s="1" t="s">
         <v>596</v>
       </c>
@@ -4790,26 +4769,24 @@
         <v>8</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="1" t="s">
-        <v>103</v>
+        <v>306</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>232</v>
+        <v>307</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>308</v>
       </c>
       <c r="E77" s="1"/>
-      <c r="F77" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="F77" s="1"/>
       <c r="G77" s="1" t="s">
         <v>596</v>
       </c>
@@ -4817,23 +4794,25 @@
         <v>8</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>283</v>
+        <v>237</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>284</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="E78" s="1"/>
+        <v>238</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="F78" s="1"/>
       <c r="G78" s="1" t="s">
         <v>596</v>
@@ -4842,21 +4821,21 @@
         <v>8</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="1" t="s">
-        <v>306</v>
+        <v>107</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>308</v>
+        <v>241</v>
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
@@ -4867,25 +4846,23 @@
         <v>8</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>284</v>
+        <v>150</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>286</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>239</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1" t="s">
         <v>596</v>
@@ -4894,77 +4871,85 @@
         <v>8</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="1" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>285</v>
+        <v>136</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="G81" s="1" t="s">
         <v>596</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>242</v>
+        <v>501</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
+        <v>257</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="G82" s="1" t="s">
         <v>596</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="1" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C83" s="5" t="s">
-        <v>255</v>
+      <c r="C83" s="2" t="s">
+        <v>287</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>68</v>
+        <v>245</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>192</v>
+        <v>246</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>596</v>
@@ -4973,84 +4958,84 @@
         <v>24</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>501</v>
+        <v>247</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="1" t="s">
-        <v>109</v>
+        <v>7</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>111</v>
+        <v>271</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>112</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="F84" s="1"/>
       <c r="G84" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>136</v>
+        <v>311</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>245</v>
+        <v>281</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>246</v>
+        <v>203</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F86" s="1"/>
+        <v>164</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="G86" s="1" t="s">
         <v>597</v>
       </c>
@@ -5058,27 +5043,25 @@
         <v>8</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>253</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>281</v>
+        <v>142</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>312</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>203</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="E87" s="1"/>
       <c r="F87" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>597</v>
@@ -5087,28 +5070,24 @@
         <v>8</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>141</v>
+        <v>313</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
       <c r="G88" s="1" t="s">
         <v>597</v>
       </c>
@@ -5116,26 +5095,22 @@
         <v>8</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>322</v>
+        <v>18</v>
+      </c>
+      <c r="B89" s="1"/>
+      <c r="C89" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="E89" s="1"/>
-      <c r="F89" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="F89" s="1"/>
       <c r="G89" s="1" t="s">
         <v>597</v>
       </c>
@@ -5143,21 +5118,19 @@
         <v>8</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>187</v>
+        <v>222</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>313</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B90" s="1"/>
       <c r="C90" s="2" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>291</v>
+        <v>21</v>
       </c>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
@@ -5168,42 +5141,50 @@
         <v>8</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>188</v>
+        <v>223</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B91" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="C91" s="2" t="s">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
+        <v>245</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="G91" s="1" t="s">
         <v>597</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B92" s="1"/>
-      <c r="C92" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>314</v>
       </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
@@ -5214,28 +5195,24 @@
         <v>8</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="1" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>23</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
       <c r="G93" s="1" t="s">
         <v>597</v>
       </c>
@@ -5243,69 +5220,71 @@
         <v>24</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>247</v>
+        <v>202</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>314</v>
+        <v>72</v>
+      </c>
+      <c r="B94" s="1"/>
+      <c r="C94" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>254</v>
+        <v>197</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="1" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>26</v>
+        <v>250</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
+      <c r="F95" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="G95" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>202</v>
+        <v>249</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B96" s="1"/>
+        <v>127</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>309</v>
+      </c>
       <c r="C96" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>198</v>
+        <v>310</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
@@ -5313,137 +5292,119 @@
         <v>598</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>250</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="B97" s="1"/>
       <c r="C97" s="2" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>248</v>
+        <v>74</v>
       </c>
       <c r="E97" s="1"/>
-      <c r="F97" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="F97" s="1"/>
       <c r="G97" s="1" t="s">
         <v>598</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>249</v>
+        <v>201</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="1" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>309</v>
+        <v>151</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>26</v>
+        <v>273</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="E98" s="1"/>
-      <c r="F98" s="1"/>
+      <c r="F98" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="G98" s="1" t="s">
         <v>598</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>202</v>
+        <v>8</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="99" spans="1:9">
-      <c r="A99" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B99" s="1"/>
-      <c r="C99" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="H99" s="1" t="s">
+      <c r="A99" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="H99" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>201</v>
+        <v>349</v>
       </c>
     </row>
     <row r="100" spans="1:9">
-      <c r="A100" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>561</v>
+      <c r="A100" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>592</v>
@@ -5452,15 +5413,15 @@
         <v>8</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>592</v>
@@ -5469,41 +5430,53 @@
         <v>8</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="2" t="s">
-        <v>354</v>
+        <v>371</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>372</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>358</v>
+        <v>373</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>378</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I104" s="1" t="s">
-        <v>359</v>
+      <c r="I104" s="13" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="2" t="s">
-        <v>355</v>
+        <v>371</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>372</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>360</v>
+        <v>373</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>378</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I105" s="1" t="s">
-        <v>361</v>
+      <c r="I105" s="13" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -5519,8 +5492,8 @@
       <c r="E106" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="G106" s="2" t="s">
-        <v>601</v>
+      <c r="G106" s="1" t="s">
+        <v>602</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>8</v>
@@ -5542,8 +5515,8 @@
       <c r="E107" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="G107" s="2" t="s">
-        <v>604</v>
+      <c r="G107" s="1" t="s">
+        <v>603</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>8</v>
@@ -5566,7 +5539,7 @@
         <v>378</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>8</v>
@@ -5577,160 +5550,172 @@
     </row>
     <row r="109" spans="1:9">
       <c r="A109" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>372</v>
+        <v>375</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>376</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>378</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I109" s="13" t="s">
-        <v>374</v>
+      <c r="I109" s="1" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="110" spans="1:9">
-      <c r="A110" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>373</v>
+      <c r="A110" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>381</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>378</v>
+        <v>331</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I110" s="13" t="s">
-        <v>374</v>
+        <v>594</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>378</v>
+        <v>331</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="H111" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="H111" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="112" spans="1:9">
-      <c r="A112" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>381</v>
+      <c r="A112" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>388</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I112" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9">
-      <c r="A113" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>383</v>
+        <v>389</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I112" s="15" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="23.45" customHeight="1">
+      <c r="A113" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G113" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="H113" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I113" s="12" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="114" spans="1:9">
-      <c r="A114" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="H114" s="2" t="s">
+      <c r="A114" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="B114" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="G114" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="H114" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="I114" s="15" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" ht="23.4" customHeight="1">
+      <c r="I114" s="12" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
       <c r="A115" s="12" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="C115" s="12" t="s">
-        <v>393</v>
+        <v>404</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>405</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>396</v>
+        <v>113</v>
       </c>
       <c r="G115" s="12" t="s">
         <v>599</v>
@@ -5739,227 +5724,212 @@
         <v>8</v>
       </c>
       <c r="I115" s="12" t="s">
-        <v>397</v>
+        <v>561</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="12" t="s">
-        <v>398</v>
-      </c>
-      <c r="B116" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>400</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="B116" s="5"/>
+      <c r="C116" s="12"/>
       <c r="D116" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="E116" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="G116" s="12" t="s">
-        <v>599</v>
+        <v>409</v>
+      </c>
+      <c r="E116" s="12"/>
+      <c r="F116" s="12"/>
+      <c r="G116" s="1" t="s">
+        <v>593</v>
       </c>
       <c r="H116" s="12" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I116" s="12" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" s="12" t="s">
-        <v>155</v>
+        <v>411</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="E117" s="6" t="s">
-        <v>407</v>
+        <v>414</v>
+      </c>
+      <c r="E117" s="12" t="s">
+        <v>424</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G117" s="12" t="s">
-        <v>599</v>
+        <v>415</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>593</v>
       </c>
       <c r="H117" s="12" t="s">
         <v>8</v>
       </c>
       <c r="I117" s="12" t="s">
-        <v>561</v>
+        <v>416</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="12" t="s">
-        <v>408</v>
-      </c>
-      <c r="B118" s="5"/>
-      <c r="C118" s="12"/>
+        <v>417</v>
+      </c>
+      <c r="B118" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>419</v>
+      </c>
       <c r="D118" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="E118" s="12"/>
-      <c r="F118" s="12"/>
-      <c r="G118" s="1" t="s">
-        <v>593</v>
+        <v>420</v>
+      </c>
+      <c r="E118" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="F118" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="G118" s="12" t="s">
+        <v>590</v>
       </c>
       <c r="H118" s="12" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I118" s="12" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
     </row>
     <row r="119" spans="1:9">
-      <c r="A119" s="12" t="s">
-        <v>411</v>
-      </c>
-      <c r="B119" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="D119" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="E119" s="12" t="s">
-        <v>424</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>415</v>
+      <c r="A119" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="H119" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="I119" s="12" t="s">
-        <v>416</v>
+        <v>75</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="120" spans="1:9">
-      <c r="A120" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="B120" s="12" t="s">
-        <v>418</v>
+      <c r="A120" s="2" t="s">
+        <v>431</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="D120" s="12" t="s">
-        <v>420</v>
-      </c>
-      <c r="E120" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="F120" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="G120" s="12" t="s">
-        <v>590</v>
-      </c>
-      <c r="H120" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I120" s="12" t="s">
-        <v>421</v>
+        <v>432</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>427</v>
+        <v>431</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>432</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>344</v>
+        <v>433</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>75</v>
+        <v>604</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="122" spans="1:9">
-      <c r="A122" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>433</v>
+      <c r="A122" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>437</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="123" spans="1:9">
-      <c r="A123" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>433</v>
+      <c r="A123" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>442</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
     </row>
     <row r="124" spans="1:9">
-      <c r="A124" s="13" t="s">
-        <v>435</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="D124" s="13" t="s">
-        <v>437</v>
+      <c r="A124" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B124" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>446</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>596</v>
@@ -5968,21 +5938,24 @@
         <v>8</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
     </row>
     <row r="125" spans="1:9">
-      <c r="A125" s="13" t="s">
-        <v>439</v>
+      <c r="A125" s="2" t="s">
+        <v>473</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>440</v>
+        <v>448</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>449</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="F125" s="7" t="s">
-        <v>442</v>
+        <v>450</v>
+      </c>
+      <c r="F125" s="16" t="s">
+        <v>451</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>596</v>
@@ -5990,19 +5963,25 @@
       <c r="H125" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I125" s="1" t="s">
-        <v>443</v>
-      </c>
     </row>
     <row r="126" spans="1:9">
-      <c r="A126" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="B126" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>446</v>
+      <c r="A126" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>455</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>596</v>
@@ -6011,148 +5990,151 @@
         <v>8</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
     </row>
     <row r="127" spans="1:9">
-      <c r="A127" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>449</v>
+      <c r="A127" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>459</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="F127" s="16" t="s">
-        <v>451</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="F127" s="8"/>
       <c r="G127" s="1" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>8</v>
+      </c>
+      <c r="I127" s="17" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>453</v>
+        <v>462</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>463</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="E128" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="F128" s="7" t="s">
-        <v>455</v>
+        <v>465</v>
+      </c>
+      <c r="E128" s="7"/>
+      <c r="F128" s="13" t="s">
+        <v>466</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
     </row>
     <row r="129" spans="1:9">
-      <c r="A129" s="7" t="s">
-        <v>490</v>
-      </c>
-      <c r="B129" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="C129" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="D129" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="E129" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="F129" s="8"/>
+      <c r="A129" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="E129" s="7"/>
       <c r="G129" s="1" t="s">
         <v>593</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I129" s="17" t="s">
-        <v>489</v>
+      <c r="I129" s="1" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="130" spans="1:9">
-      <c r="A130" s="7" t="s">
-        <v>462</v>
+      <c r="A130" s="2" t="s">
+        <v>478</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="D130" s="13" t="s">
-        <v>465</v>
-      </c>
-      <c r="E130" s="7"/>
-      <c r="F130" s="13" t="s">
-        <v>466</v>
+        <v>481</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>593</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I130" s="1" t="s">
-        <v>467</v>
+        <v>24</v>
+      </c>
+      <c r="I130" s="17" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" s="2" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="D131" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="E131" s="7"/>
+        <v>257</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>483</v>
+      </c>
       <c r="G131" s="1" t="s">
         <v>593</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>472</v>
+        <v>24</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="132" spans="1:9">
-      <c r="A132" s="2" t="s">
-        <v>478</v>
+      <c r="A132" s="9" t="s">
+        <v>484</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>481</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>488</v>
@@ -6160,196 +6142,195 @@
       <c r="F132" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G132" s="1" t="s">
+      <c r="G132" s="2" t="s">
         <v>593</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I132" s="17" t="s">
-        <v>479</v>
+      <c r="I132" s="2" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="133" spans="1:9">
-      <c r="A133" s="2" t="s">
-        <v>480</v>
+      <c r="A133" s="10" t="s">
+        <v>495</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>257</v>
+        <v>494</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>593</v>
+        <v>492</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>592</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="134" spans="1:9">
-      <c r="A134" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>481</v>
+      <c r="A134" s="18" t="s">
+        <v>499</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="F134" s="5" t="s">
-        <v>46</v>
+        <v>498</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>497</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>24</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
     </row>
     <row r="135" spans="1:9">
-      <c r="A135" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>493</v>
+      <c r="A135" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C135" s="11" t="s">
+        <v>511</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>492</v>
+        <v>503</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>504</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I135" s="2" t="s">
-        <v>491</v>
+      <c r="I135" s="1" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="136" spans="1:9">
-      <c r="A136" s="18" t="s">
-        <v>499</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="G136" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I136" s="2" t="s">
-        <v>496</v>
+      <c r="A136" s="13" t="s">
+        <v>506</v>
+      </c>
+      <c r="B136" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="C136" s="11" t="s">
+        <v>512</v>
+      </c>
+      <c r="D136" s="11" t="s">
+        <v>508</v>
+      </c>
+      <c r="E136" s="13" t="s">
+        <v>509</v>
+      </c>
+      <c r="F136" s="13"/>
+      <c r="G136" s="13" t="s">
+        <v>601</v>
+      </c>
+      <c r="H136" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="I136" s="13" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="C137" s="11" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I137" s="1" t="s">
-        <v>505</v>
+      <c r="I137" s="2" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="138" spans="1:9">
-      <c r="A138" s="13" t="s">
-        <v>506</v>
-      </c>
-      <c r="B138" s="13" t="s">
-        <v>507</v>
-      </c>
-      <c r="C138" s="11" t="s">
-        <v>512</v>
+      <c r="A138" s="2" t="s">
+        <v>518</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>508</v>
-      </c>
-      <c r="E138" s="13" t="s">
-        <v>509</v>
-      </c>
-      <c r="F138" s="13"/>
-      <c r="G138" s="13" t="s">
-        <v>601</v>
-      </c>
-      <c r="H138" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="I138" s="13" t="s">
-        <v>510</v>
+        <v>519</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="139" spans="1:9">
-      <c r="A139" s="2" t="s">
-        <v>516</v>
+      <c r="A139" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B139" s="1"/>
+      <c r="C139" s="3" t="s">
+        <v>477</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="G139" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="H139" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I139" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="140" spans="1:9">
-      <c r="A140" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="D140" s="11" t="s">
-        <v>519</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="H140" s="2" t="s">
+      <c r="A140" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B140" s="1"/>
+      <c r="C140" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="H140" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -6370,7 +6351,7 @@
         <v>474</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="H141" s="1" t="s">
         <v>8</v>
@@ -6397,7 +6378,7 @@
         <v>474</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>8</v>
@@ -6424,7 +6405,7 @@
         <v>474</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="H143" s="1" t="s">
         <v>8</v>
@@ -6434,74 +6415,72 @@
       </c>
     </row>
     <row r="144" spans="1:9">
-      <c r="A144" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="B144" s="1"/>
-      <c r="C144" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="G144" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="H144" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I144" s="1" t="s">
-        <v>522</v>
+      <c r="A144" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D144" s="11" t="s">
+        <v>562</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I144" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="145" spans="1:9">
-      <c r="A145" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="B145" s="1"/>
-      <c r="C145" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="F145" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="H145" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I145" s="1" t="s">
-        <v>522</v>
+      <c r="A145" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B145" s="19" t="s">
+        <v>530</v>
+      </c>
+      <c r="C145" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="D145" s="11" t="s">
+        <v>531</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I145" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="146" spans="1:9">
       <c r="A146" s="2" t="s">
-        <v>523</v>
+        <v>563</v>
+      </c>
+      <c r="B146" s="19" t="s">
+        <v>530</v>
+      </c>
+      <c r="C146" s="11" t="s">
+        <v>554</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>562</v>
+        <v>531</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>532</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -6521,7 +6500,7 @@
         <v>532</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>8</v>
@@ -6546,8 +6525,8 @@
       <c r="E148" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="G148" s="2" t="s">
-        <v>593</v>
+      <c r="G148" s="1" t="s">
+        <v>596</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>8</v>
@@ -6572,8 +6551,8 @@
       <c r="E149" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="G149" s="2" t="s">
-        <v>600</v>
+      <c r="G149" s="1" t="s">
+        <v>601</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>8</v>
@@ -6584,126 +6563,129 @@
     </row>
     <row r="150" spans="1:9">
       <c r="A150" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="B150" s="19" t="s">
-        <v>530</v>
+        <v>525</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>534</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>532</v>
+        <v>536</v>
+      </c>
+      <c r="F150" s="11" t="s">
+        <v>537</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I150" t="s">
-        <v>533</v>
+        <v>24</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="151" spans="1:9">
       <c r="A151" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="B151" s="19" t="s">
-        <v>530</v>
-      </c>
-      <c r="C151" s="11" t="s">
-        <v>554</v>
+        <v>526</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>539</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>601</v>
+        <v>344</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>598</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I151" t="s">
-        <v>533</v>
+      <c r="I151" s="1" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="152" spans="1:9">
       <c r="A152" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>537</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>598</v>
+        <v>545</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>590</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>24</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="153" spans="1:9">
       <c r="A153" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>539</v>
+        <v>559</v>
+      </c>
+      <c r="C153" s="11" t="s">
+        <v>557</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>344</v>
+        <v>548</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
     </row>
     <row r="154" spans="1:9">
       <c r="A154" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D154" s="11" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="F154" s="11" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>590</v>
@@ -6712,242 +6694,229 @@
         <v>24</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
     </row>
     <row r="155" spans="1:9">
-      <c r="A155" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="C155" s="11" t="s">
-        <v>557</v>
-      </c>
-      <c r="D155" s="11" t="s">
-        <v>547</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>548</v>
+      <c r="A155" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="B155" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D155" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="E155" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="F155" s="20" t="s">
+        <v>564</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="H155" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I155" s="1" t="s">
-        <v>549</v>
+        <v>600</v>
+      </c>
+      <c r="H155" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I155" s="12" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:9">
       <c r="A156" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>560</v>
+        <v>502</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="D156" s="11" t="s">
-        <v>550</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="F156" s="11" t="s">
-        <v>552</v>
+        <v>511</v>
+      </c>
+      <c r="D156" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>504</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="H156" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="A157" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B157" s="21"/>
+      <c r="D157" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="H157" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I156" s="1" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9">
-      <c r="A157" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="B157" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="D157" s="12" t="s">
-        <v>420</v>
-      </c>
-      <c r="E157" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="F157" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="G157" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="H157" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I157" s="12" t="s">
-        <v>421</v>
+      <c r="I157" s="1" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="158" spans="1:9">
       <c r="A158" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="C158" s="11" t="s">
-        <v>511</v>
-      </c>
-      <c r="D158" s="20" t="s">
-        <v>503</v>
-      </c>
-      <c r="F158" s="2" t="s">
-        <v>504</v>
+        <v>570</v>
+      </c>
+      <c r="B158" s="21"/>
+      <c r="C158" s="20" t="s">
+        <v>573</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I158" s="1" t="s">
-        <v>505</v>
+      <c r="I158" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="159" spans="1:9">
-      <c r="A159" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="B159" s="21"/>
-      <c r="D159" s="20" t="s">
-        <v>566</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>344</v>
+      <c r="A159" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="B159" t="s">
+        <v>576</v>
+      </c>
+      <c r="C159" s="20" t="s">
+        <v>574</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="F159" s="20" t="s">
+        <v>575</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>24</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>565</v>
+        <v>579</v>
       </c>
     </row>
     <row r="160" spans="1:9">
-      <c r="A160" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="B160" s="21"/>
-      <c r="C160" s="20" t="s">
-        <v>573</v>
-      </c>
-      <c r="D160" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>344</v>
+      <c r="A160" s="13" t="s">
+        <v>577</v>
+      </c>
+      <c r="C160" t="s">
+        <v>587</v>
+      </c>
+      <c r="D160" s="20" t="s">
+        <v>578</v>
+      </c>
+      <c r="F160" s="20" t="s">
+        <v>586</v>
       </c>
       <c r="G160" s="2" t="s">
         <v>596</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I160" t="s">
-        <v>569</v>
+        <v>24</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="161" spans="1:9">
-      <c r="A161" s="13" t="s">
-        <v>571</v>
-      </c>
-      <c r="B161" t="s">
-        <v>576</v>
-      </c>
-      <c r="C161" s="20" t="s">
-        <v>574</v>
+      <c r="A161" s="2" t="s">
+        <v>581</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="F161" s="20" t="s">
-        <v>575</v>
-      </c>
       <c r="G161" s="2" t="s">
         <v>590</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I161" s="1" t="s">
-        <v>579</v>
+      <c r="I161" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="162" spans="1:9">
-      <c r="A162" s="13" t="s">
-        <v>577</v>
-      </c>
-      <c r="C162" t="s">
-        <v>587</v>
+      <c r="A162" s="2" t="s">
+        <v>584</v>
       </c>
       <c r="D162" s="20" t="s">
-        <v>578</v>
-      </c>
-      <c r="F162" s="20" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>572</v>
+        <v>567</v>
+      </c>
+      <c r="B163" s="21"/>
+      <c r="D163" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I163" t="s">
-        <v>582</v>
+      <c r="I163" s="1" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="164" spans="1:9">
       <c r="A164" s="2" t="s">
-        <v>584</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="B164" s="21"/>
       <c r="D164" s="20" t="s">
-        <v>583</v>
+        <v>566</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>585</v>
+        <v>565</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -6955,6 +6924,7 @@
         <v>567</v>
       </c>
       <c r="B165" s="21"/>
+      <c r="C165" s="20"/>
       <c r="D165" s="20" t="s">
         <v>566</v>
       </c>
@@ -6962,7 +6932,7 @@
         <v>344</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>24</v>
@@ -6973,45 +6943,50 @@
     </row>
     <row r="166" spans="1:9">
       <c r="A166" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B166" s="21"/>
+      <c r="C166" s="20" t="s">
+        <v>588</v>
+      </c>
       <c r="D166" s="20" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>344</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I166" s="1" t="s">
-        <v>565</v>
+        <v>8</v>
+      </c>
+      <c r="I166" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="167" spans="1:9">
       <c r="A167" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B167" s="21"/>
-      <c r="C167" s="20"/>
+      <c r="C167" s="20" t="s">
+        <v>588</v>
+      </c>
       <c r="D167" s="20" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>344</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I167" s="1" t="s">
-        <v>565</v>
+        <v>8</v>
+      </c>
+      <c r="I167" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -7029,7 +7004,7 @@
         <v>344</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>8</v>
@@ -7053,7 +7028,7 @@
         <v>344</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>8</v>
@@ -7062,192 +7037,140 @@
         <v>569</v>
       </c>
     </row>
-    <row r="170" spans="1:9">
-      <c r="A170" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="B170" s="21"/>
-      <c r="C170" s="20" t="s">
-        <v>588</v>
-      </c>
-      <c r="D170" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="G170" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="H170" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I170" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9">
-      <c r="A171" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="B171" s="21"/>
-      <c r="C171" s="20" t="s">
-        <v>588</v>
-      </c>
-      <c r="D171" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="G171" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="H171" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I171" t="s">
-        <v>569</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:I100">
-    <sortCondition ref="G4:G100"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I98">
+    <sortCondition ref="G2:G98"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="F25" r:id="rId1" xr:uid="{56461029-F272-40B0-AA7C-85F66C5CF6EB}"/>
-    <hyperlink ref="F58" r:id="rId2" xr:uid="{94D7D8F8-44B5-447E-9A32-9F64E5CCF3FA}"/>
-    <hyperlink ref="C80" r:id="rId3" xr:uid="{777A5BAE-8D61-4AA7-9259-E54BD1FDBE70}"/>
-    <hyperlink ref="C83" r:id="rId4" xr:uid="{FD026EBB-4302-4206-B780-7E1F91763261}"/>
-    <hyperlink ref="C67" r:id="rId5" xr:uid="{8966019B-4C3B-4F02-A071-5411CA74F3F8}"/>
-    <hyperlink ref="D84" r:id="rId6" xr:uid="{F64C67D3-CAF8-47D7-9BBD-60BA8702A9B2}"/>
-    <hyperlink ref="D4" r:id="rId7" xr:uid="{5E75608C-EF4E-4E89-BFD2-9C98C2096B20}"/>
-    <hyperlink ref="D6" r:id="rId8" xr:uid="{5E90B8DC-AD77-4B67-993E-32CF4C9CFD26}"/>
-    <hyperlink ref="D48" r:id="rId9" xr:uid="{097C0E3E-0A06-4C08-8729-6EE0824D62F8}"/>
-    <hyperlink ref="D98" r:id="rId10" xr:uid="{6FC1A61E-CA39-4E3B-A451-51C002A830C8}"/>
-    <hyperlink ref="D95" r:id="rId11" xr:uid="{AF63B350-6BD5-4890-B968-9E23CBF2D9C4}"/>
-    <hyperlink ref="D87" r:id="rId12" xr:uid="{68410040-0123-49F9-AD96-D8FBAF000148}"/>
-    <hyperlink ref="D51" r:id="rId13" location="programs " xr:uid="{9E90FFD4-3789-45CA-8EE0-D02F471C3648}"/>
-    <hyperlink ref="D52" r:id="rId14" xr:uid="{5DADD7F9-891C-4DA9-8630-2E4F57BA4BB0}"/>
-    <hyperlink ref="D76" r:id="rId15" xr:uid="{E7FCC05F-E0C4-4B4B-9BF6-3D5388C2BBD3}"/>
-    <hyperlink ref="D60" r:id="rId16" xr:uid="{BA7221EF-B2F7-48AC-BA37-4D01E6B77745}"/>
-    <hyperlink ref="D25" r:id="rId17" xr:uid="{94B72A5A-DA9F-4A49-B6D6-869D1EB3A773}"/>
-    <hyperlink ref="D59" r:id="rId18" xr:uid="{D1114FE8-20D3-4F80-B444-5686CFBB7223}"/>
-    <hyperlink ref="D58" r:id="rId19" xr:uid="{4A5896AC-FF3D-4F52-9EEA-57FA7C298A0F}"/>
-    <hyperlink ref="D57" r:id="rId20" xr:uid="{EB5F5F74-D4A1-4286-B2C3-3B240C8A0B3A}"/>
-    <hyperlink ref="D56" r:id="rId21" xr:uid="{A4E9F103-D8DF-4A08-B73B-82C9402281E0}"/>
-    <hyperlink ref="D53" r:id="rId22" xr:uid="{7C9B8008-6FC3-4D8B-9FAC-859864B3CCA6}"/>
-    <hyperlink ref="D61" r:id="rId23" xr:uid="{8B92366E-1104-40D7-B41A-5F9D960F675C}"/>
-    <hyperlink ref="D62" r:id="rId24" xr:uid="{BA61B788-1EE1-4D0A-BE68-5496335960B2}"/>
-    <hyperlink ref="D63" r:id="rId25" xr:uid="{788ED0D2-F799-42C7-BE70-26DAA5615100}"/>
-    <hyperlink ref="D64" r:id="rId26" xr:uid="{5315C9E9-D76A-423C-BFE1-AF451A0BCC1E}"/>
-    <hyperlink ref="D65" r:id="rId27" xr:uid="{BC82856E-908A-45D9-A41B-408B8FC5E720}"/>
-    <hyperlink ref="D66" r:id="rId28" xr:uid="{BFEA5820-6FEF-4AB5-AFDC-035AB404A7DA}"/>
-    <hyperlink ref="D67" r:id="rId29" xr:uid="{76669F61-A905-4387-B0E8-34E4D1366C7B}"/>
-    <hyperlink ref="D68" r:id="rId30" xr:uid="{74F9C236-EE46-491C-BF5A-2DFA889F7A26}"/>
-    <hyperlink ref="D69" r:id="rId31" xr:uid="{C8AC3248-2D61-4C9F-9CC4-96E24312EBEA}"/>
-    <hyperlink ref="D70" r:id="rId32" xr:uid="{B26C8AAE-4B11-4F8E-B74E-F7458BF05D09}"/>
-    <hyperlink ref="D71" r:id="rId33" xr:uid="{2A1A49A2-F37D-4774-AE8D-F594F26111D7}"/>
-    <hyperlink ref="D72" r:id="rId34" xr:uid="{9B7A9104-CDE8-4FC8-A2F3-845B8C3DB23E}"/>
-    <hyperlink ref="D73" r:id="rId35" xr:uid="{CF5BDF24-B56F-4FFF-B0DB-92F7D035BE83}"/>
-    <hyperlink ref="D74" r:id="rId36" xr:uid="{42118767-4820-49B5-A394-949C14367612}"/>
-    <hyperlink ref="D75" r:id="rId37" xr:uid="{B2C0A57F-0293-4754-8D4A-7C784AF7C213}"/>
-    <hyperlink ref="D77" r:id="rId38" xr:uid="{D07F3365-A219-44A8-BDED-0A41BC7D7571}"/>
-    <hyperlink ref="D43" r:id="rId39" xr:uid="{019C03B9-1170-401E-B03B-C29FC6CF108A}"/>
-    <hyperlink ref="C43" r:id="rId40" xr:uid="{33BA4AA8-12EB-4D42-B2D2-FB4088026AE5}"/>
-    <hyperlink ref="C18" r:id="rId41" xr:uid="{05C5E1C3-5F61-4D07-9629-20A9D90C9635}"/>
-    <hyperlink ref="C95" r:id="rId42" xr:uid="{FDB1E1E6-ADD8-4564-8753-565B078034C8}"/>
-    <hyperlink ref="D89" r:id="rId43" xr:uid="{D469BF19-F67A-4157-A0FF-1AA4B9E0BF23}"/>
-    <hyperlink ref="D37" r:id="rId44" xr:uid="{D2E0A897-D81C-4125-9C47-3A8C879089DB}"/>
-    <hyperlink ref="C37" r:id="rId45" xr:uid="{B62AA879-0896-4DFB-BBCE-B7490B146B3E}"/>
-    <hyperlink ref="C89" r:id="rId46" xr:uid="{9F59640A-1CEF-4A8B-B161-21254F4837CD}"/>
-    <hyperlink ref="D94" r:id="rId47" xr:uid="{863F960F-332F-4E54-B6FE-24604DF43AE0}"/>
-    <hyperlink ref="D49" r:id="rId48" xr:uid="{1625DFE4-6C48-4A82-8811-F4EEB64C2D2F}"/>
-    <hyperlink ref="C49" r:id="rId49" xr:uid="{7C99B3A7-0A0D-4CE1-93C6-1839F51BF301}"/>
-    <hyperlink ref="C94" r:id="rId50" xr:uid="{450BC70E-87BA-43CB-B09E-27FB7290B23E}"/>
-    <hyperlink ref="D54" r:id="rId51" xr:uid="{968FB6ED-3EE3-4000-9ED4-DED4170844E0}"/>
-    <hyperlink ref="D55" r:id="rId52" xr:uid="{F95FFAFA-D649-4148-ACBF-893459976BA3}"/>
-    <hyperlink ref="D30" r:id="rId53" xr:uid="{867A5CA1-DED0-4BC8-AA9D-0AC38C76154A}"/>
-    <hyperlink ref="C30" r:id="rId54" xr:uid="{33C23722-2292-452E-A86A-F2FF5F22AC03}"/>
-    <hyperlink ref="C19" r:id="rId55" xr:uid="{F89D664A-980E-4238-B48D-9E9A504E1383}"/>
-    <hyperlink ref="C106" r:id="rId56" xr:uid="{51C929CE-DB05-4DB6-84D8-85DAEC31CA86}"/>
-    <hyperlink ref="C107" r:id="rId57" xr:uid="{9F47A25C-362F-482B-B273-28CEF5F32C42}"/>
-    <hyperlink ref="C108" r:id="rId58" xr:uid="{64711161-99CC-43DD-9210-5E37A90E2DC5}"/>
-    <hyperlink ref="C109" r:id="rId59" xr:uid="{DF29EEE0-9F8D-4CF7-A923-7DC294F875C1}"/>
-    <hyperlink ref="C110" r:id="rId60" xr:uid="{81445D97-055E-4976-A30D-35BCE81CA70D}"/>
-    <hyperlink ref="D112" r:id="rId61" xr:uid="{693DB290-21F0-4514-9B8B-A8622C7B663B}"/>
-    <hyperlink ref="C114" r:id="rId62" xr:uid="{D55A67DC-BCF5-42B3-A86F-2339F8569063}"/>
-    <hyperlink ref="F114" r:id="rId63" display="mailto:career@albany.edu" xr:uid="{3D51B50C-49E6-4748-8F93-05F06C5C84BC}"/>
-    <hyperlink ref="C121" r:id="rId64" xr:uid="{FCB186DB-E4AB-43E4-9D1F-D223B2641022}"/>
-    <hyperlink ref="D125" r:id="rId65" xr:uid="{480FDF2F-7B59-4251-810C-73628BB15F67}"/>
-    <hyperlink ref="D127" r:id="rId66" xr:uid="{782AF740-7E61-4A73-AC61-FACCA8448159}"/>
-    <hyperlink ref="D131" r:id="rId67" xr:uid="{E8D15C86-B9A2-49FC-8FBA-DD6355B5091B}"/>
-    <hyperlink ref="C128" r:id="rId68" xr:uid="{604F38FE-1039-4EE3-8E74-8165B8FF8430}"/>
-    <hyperlink ref="C129" r:id="rId69" xr:uid="{F0014F07-00B7-439A-9BE1-6BAE3ECD85AC}"/>
-    <hyperlink ref="C130" r:id="rId70" xr:uid="{82004575-EEEF-4DDF-972C-9340A1AA43F5}"/>
-    <hyperlink ref="C127" r:id="rId71" xr:uid="{74182992-2721-4728-8FE1-43CF72383D38}"/>
-    <hyperlink ref="C131" r:id="rId72" xr:uid="{7EBFD176-16F3-4D24-9E15-870D3D96750B}"/>
-    <hyperlink ref="F143" r:id="rId73" xr:uid="{0F9AD5BE-0C46-4CBA-ABED-01801389D4B4}"/>
-    <hyperlink ref="C143" r:id="rId74" xr:uid="{7488EE3C-4876-41B7-AD1C-E59148EF5C60}"/>
-    <hyperlink ref="F145" r:id="rId75" xr:uid="{94D425E2-BDB7-40FE-AC8D-A0E405381B9B}"/>
-    <hyperlink ref="C145" r:id="rId76" xr:uid="{8771AA61-5955-4023-916F-EA0D148D2A7D}"/>
-    <hyperlink ref="F144" r:id="rId77" xr:uid="{6E99B26B-E909-48C3-BA3B-0EEAB27C601B}"/>
-    <hyperlink ref="C144" r:id="rId78" xr:uid="{EEB16B9A-E1D2-47F9-8980-91086F1C74C7}"/>
-    <hyperlink ref="F141" r:id="rId79" xr:uid="{68D944DA-C5C2-4839-8C79-F0953BD9134E}"/>
-    <hyperlink ref="C141" r:id="rId80" xr:uid="{E8AB3E9D-8C94-415D-AB28-D7CA4C6F6343}"/>
-    <hyperlink ref="F142" r:id="rId81" xr:uid="{F3CC3505-39D1-4EEA-8FA9-8AAB6F9BF146}"/>
-    <hyperlink ref="C142" r:id="rId82" xr:uid="{7A6FF923-3DFA-4E0B-A15D-03D091C92A64}"/>
-    <hyperlink ref="C133" r:id="rId83" xr:uid="{1FA6BB05-074A-4060-BBBF-C2C63D7C12FC}"/>
-    <hyperlink ref="F132" r:id="rId84" xr:uid="{59790EAE-256A-42B0-A297-EC57CF947976}"/>
-    <hyperlink ref="F134" r:id="rId85" xr:uid="{F171B7C9-73EF-4309-8CB2-15FCE8C2CC9E}"/>
-    <hyperlink ref="D129" r:id="rId86" xr:uid="{AE4C7754-0BC6-4329-BE3F-677BC8B998A9}"/>
-    <hyperlink ref="D138" r:id="rId87" xr:uid="{9B78D813-C58E-43B6-93FE-BA5C85BE774B}"/>
-    <hyperlink ref="C137" r:id="rId88" xr:uid="{5EA92CD5-A670-4F7D-BE25-D144C30E8390}"/>
-    <hyperlink ref="C138" r:id="rId89" xr:uid="{04A96344-FBF4-45CD-BF8A-74E2E9E7A1D4}"/>
-    <hyperlink ref="D140" r:id="rId90" xr:uid="{E6E27C26-8B3F-4E6E-A7F0-56D080F5A059}"/>
-    <hyperlink ref="D147" r:id="rId91" xr:uid="{72104B61-6124-4681-83A2-C04FE8A81422}"/>
-    <hyperlink ref="D152" r:id="rId92" xr:uid="{E34F98A6-233F-4D98-AA31-6A6F8739EE10}"/>
-    <hyperlink ref="F152" r:id="rId93" xr:uid="{F2B73996-B1DF-4B50-B7BF-4A8DAC2EBCF8}"/>
-    <hyperlink ref="D153" r:id="rId94" xr:uid="{E9C2E3C3-D837-4EED-B479-25B788589D5C}"/>
-    <hyperlink ref="F154" r:id="rId95" xr:uid="{B8E43DA3-B50D-4D55-8A39-449316C19072}"/>
-    <hyperlink ref="D154" r:id="rId96" xr:uid="{93C67D5A-182E-44E5-98F0-C26DAA38348E}"/>
-    <hyperlink ref="D155" r:id="rId97" xr:uid="{EB6504E0-5D02-48B9-AA8E-AD172B0786CC}"/>
-    <hyperlink ref="F156" r:id="rId98" xr:uid="{F6FEA5C8-2D79-4B3D-8A2D-56E7162EDEEF}"/>
-    <hyperlink ref="D156" r:id="rId99" xr:uid="{5E9ADF47-E415-42D0-96AD-AC14CEFDB46A}"/>
-    <hyperlink ref="C147" r:id="rId100" xr:uid="{8F9F1B99-EA6C-4B9C-A2F0-0A5ADEB1AAC5}"/>
-    <hyperlink ref="C148" r:id="rId101" xr:uid="{7DDADF0B-37EF-456E-A584-90A75DC8E532}"/>
-    <hyperlink ref="C149" r:id="rId102" xr:uid="{4DBCE484-8796-477B-9C75-E13EC16BE78D}"/>
-    <hyperlink ref="C150" r:id="rId103" xr:uid="{4B652928-E776-4C62-81AB-B3F682C91A9B}"/>
-    <hyperlink ref="C151" r:id="rId104" xr:uid="{263071B5-2297-41D5-BD0E-1DD5BC8884ED}"/>
-    <hyperlink ref="D148:D151" r:id="rId105" display="https://www.risse-albany.org/" xr:uid="{281154D0-8EC0-4929-9B07-64C9F15DC597}"/>
-    <hyperlink ref="C152" r:id="rId106" xr:uid="{B16923BE-F0C3-427E-9F10-6F9A519FC287}"/>
-    <hyperlink ref="C154" r:id="rId107" xr:uid="{E132F971-9DCB-4C0F-937B-6476DE4ACCAD}"/>
-    <hyperlink ref="C155" r:id="rId108" xr:uid="{A00E4B55-C978-401C-8846-DB1632284D50}"/>
-    <hyperlink ref="C156" r:id="rId109" xr:uid="{7C2DE1D7-47ED-40CF-937D-415B2488F028}"/>
-    <hyperlink ref="C158" r:id="rId110" xr:uid="{B28590EE-4458-4CAE-AE78-9975E73BC873}"/>
-    <hyperlink ref="D158" r:id="rId111" xr:uid="{1E66DBCC-AB5E-4E32-804B-D7193FA752EE}"/>
-    <hyperlink ref="F120" r:id="rId112" xr:uid="{7369515B-3200-4C5D-8DBA-683E7EA7089D}"/>
-    <hyperlink ref="F157" r:id="rId113" xr:uid="{F7A76B19-1F37-4DF5-BD65-E0CE94052793}"/>
-    <hyperlink ref="C161" r:id="rId114" display="tel:518-442-3943" xr:uid="{FF797009-0F9E-2A4A-A3A7-106BF4E6C3BA}"/>
-    <hyperlink ref="C160" r:id="rId115" xr:uid="{39AC894D-928D-1945-B205-EC44DA75AA2F}"/>
-    <hyperlink ref="F161" r:id="rId116" display="mailto:passmentor@albany.edu" xr:uid="{92FF97A4-6BFD-2047-AFAC-29DC3A1B4E54}"/>
-    <hyperlink ref="D164" r:id="rId117" xr:uid="{3DE194FC-17EE-A649-8859-317715F43009}"/>
-    <hyperlink ref="F162" r:id="rId118" display="mailto:info@cdphpcycle.org" xr:uid="{C1021047-F2A6-0D44-921E-65780A9C7407}"/>
-    <hyperlink ref="D162" r:id="rId119" xr:uid="{0F5D7C84-6C50-814B-95E8-D5E467CA24AF}"/>
-    <hyperlink ref="C168" r:id="rId120" xr:uid="{690FD66A-CACE-F148-B4D1-FC887F23F5EC}"/>
-    <hyperlink ref="C169" r:id="rId121" xr:uid="{DA09BFEF-E59D-A74C-9D84-99944ED51719}"/>
-    <hyperlink ref="C170" r:id="rId122" xr:uid="{EF917863-B783-6746-BA4E-0B21880445D2}"/>
-    <hyperlink ref="C171" r:id="rId123" xr:uid="{D678F8DB-2E76-8645-8492-668ADDB70C30}"/>
-    <hyperlink ref="D171" r:id="rId124" xr:uid="{5539CF43-9824-C040-831E-11780C081C68}"/>
-    <hyperlink ref="D170" r:id="rId125" xr:uid="{9FF172EE-8CFA-AB47-93A1-C78BEC3D269B}"/>
-    <hyperlink ref="D169" r:id="rId126" xr:uid="{19A9ABBB-6357-F847-AEED-C41F8DD723D5}"/>
-    <hyperlink ref="D168" r:id="rId127" xr:uid="{572C4F40-4005-884C-965A-3699D5D51DD3}"/>
-    <hyperlink ref="C3" r:id="rId128" xr:uid="{5B84A66F-FCDA-4D4A-83C8-BD05BBD34DCB}"/>
-    <hyperlink ref="D3" r:id="rId129" xr:uid="{0447BF89-BCC8-4E10-85F9-CBE7F49F4825}"/>
-    <hyperlink ref="C2" r:id="rId130" xr:uid="{BB16B2C9-ED93-4AB5-A09C-96E26E039168}"/>
-    <hyperlink ref="D2" r:id="rId131" xr:uid="{EFBC5402-9831-4D37-BDB2-F305566A4EE7}"/>
+    <hyperlink ref="F23" r:id="rId1" xr:uid="{56461029-F272-40B0-AA7C-85F66C5CF6EB}"/>
+    <hyperlink ref="F56" r:id="rId2" xr:uid="{94D7D8F8-44B5-447E-9A32-9F64E5CCF3FA}"/>
+    <hyperlink ref="C78" r:id="rId3" xr:uid="{777A5BAE-8D61-4AA7-9259-E54BD1FDBE70}"/>
+    <hyperlink ref="C81" r:id="rId4" xr:uid="{FD026EBB-4302-4206-B780-7E1F91763261}"/>
+    <hyperlink ref="C65" r:id="rId5" xr:uid="{8966019B-4C3B-4F02-A071-5411CA74F3F8}"/>
+    <hyperlink ref="D82" r:id="rId6" xr:uid="{F64C67D3-CAF8-47D7-9BBD-60BA8702A9B2}"/>
+    <hyperlink ref="D2" r:id="rId7" xr:uid="{5E75608C-EF4E-4E89-BFD2-9C98C2096B20}"/>
+    <hyperlink ref="D4" r:id="rId8" xr:uid="{5E90B8DC-AD77-4B67-993E-32CF4C9CFD26}"/>
+    <hyperlink ref="D46" r:id="rId9" xr:uid="{097C0E3E-0A06-4C08-8729-6EE0824D62F8}"/>
+    <hyperlink ref="D96" r:id="rId10" xr:uid="{6FC1A61E-CA39-4E3B-A451-51C002A830C8}"/>
+    <hyperlink ref="D93" r:id="rId11" xr:uid="{AF63B350-6BD5-4890-B968-9E23CBF2D9C4}"/>
+    <hyperlink ref="D85" r:id="rId12" xr:uid="{68410040-0123-49F9-AD96-D8FBAF000148}"/>
+    <hyperlink ref="D49" r:id="rId13" location="programs " xr:uid="{9E90FFD4-3789-45CA-8EE0-D02F471C3648}"/>
+    <hyperlink ref="D50" r:id="rId14" xr:uid="{5DADD7F9-891C-4DA9-8630-2E4F57BA4BB0}"/>
+    <hyperlink ref="D74" r:id="rId15" xr:uid="{E7FCC05F-E0C4-4B4B-9BF6-3D5388C2BBD3}"/>
+    <hyperlink ref="D58" r:id="rId16" xr:uid="{BA7221EF-B2F7-48AC-BA37-4D01E6B77745}"/>
+    <hyperlink ref="D23" r:id="rId17" xr:uid="{94B72A5A-DA9F-4A49-B6D6-869D1EB3A773}"/>
+    <hyperlink ref="D57" r:id="rId18" xr:uid="{D1114FE8-20D3-4F80-B444-5686CFBB7223}"/>
+    <hyperlink ref="D56" r:id="rId19" xr:uid="{4A5896AC-FF3D-4F52-9EEA-57FA7C298A0F}"/>
+    <hyperlink ref="D55" r:id="rId20" xr:uid="{EB5F5F74-D4A1-4286-B2C3-3B240C8A0B3A}"/>
+    <hyperlink ref="D54" r:id="rId21" xr:uid="{A4E9F103-D8DF-4A08-B73B-82C9402281E0}"/>
+    <hyperlink ref="D51" r:id="rId22" xr:uid="{7C9B8008-6FC3-4D8B-9FAC-859864B3CCA6}"/>
+    <hyperlink ref="D59" r:id="rId23" xr:uid="{8B92366E-1104-40D7-B41A-5F9D960F675C}"/>
+    <hyperlink ref="D60" r:id="rId24" xr:uid="{BA61B788-1EE1-4D0A-BE68-5496335960B2}"/>
+    <hyperlink ref="D61" r:id="rId25" xr:uid="{788ED0D2-F799-42C7-BE70-26DAA5615100}"/>
+    <hyperlink ref="D62" r:id="rId26" xr:uid="{5315C9E9-D76A-423C-BFE1-AF451A0BCC1E}"/>
+    <hyperlink ref="D63" r:id="rId27" xr:uid="{BC82856E-908A-45D9-A41B-408B8FC5E720}"/>
+    <hyperlink ref="D64" r:id="rId28" xr:uid="{BFEA5820-6FEF-4AB5-AFDC-035AB404A7DA}"/>
+    <hyperlink ref="D65" r:id="rId29" xr:uid="{76669F61-A905-4387-B0E8-34E4D1366C7B}"/>
+    <hyperlink ref="D66" r:id="rId30" xr:uid="{74F9C236-EE46-491C-BF5A-2DFA889F7A26}"/>
+    <hyperlink ref="D67" r:id="rId31" xr:uid="{C8AC3248-2D61-4C9F-9CC4-96E24312EBEA}"/>
+    <hyperlink ref="D68" r:id="rId32" xr:uid="{B26C8AAE-4B11-4F8E-B74E-F7458BF05D09}"/>
+    <hyperlink ref="D69" r:id="rId33" xr:uid="{2A1A49A2-F37D-4774-AE8D-F594F26111D7}"/>
+    <hyperlink ref="D70" r:id="rId34" xr:uid="{9B7A9104-CDE8-4FC8-A2F3-845B8C3DB23E}"/>
+    <hyperlink ref="D71" r:id="rId35" xr:uid="{CF5BDF24-B56F-4FFF-B0DB-92F7D035BE83}"/>
+    <hyperlink ref="D72" r:id="rId36" xr:uid="{42118767-4820-49B5-A394-949C14367612}"/>
+    <hyperlink ref="D73" r:id="rId37" xr:uid="{B2C0A57F-0293-4754-8D4A-7C784AF7C213}"/>
+    <hyperlink ref="D75" r:id="rId38" xr:uid="{D07F3365-A219-44A8-BDED-0A41BC7D7571}"/>
+    <hyperlink ref="D41" r:id="rId39" xr:uid="{019C03B9-1170-401E-B03B-C29FC6CF108A}"/>
+    <hyperlink ref="C41" r:id="rId40" xr:uid="{33BA4AA8-12EB-4D42-B2D2-FB4088026AE5}"/>
+    <hyperlink ref="C16" r:id="rId41" xr:uid="{05C5E1C3-5F61-4D07-9629-20A9D90C9635}"/>
+    <hyperlink ref="C93" r:id="rId42" xr:uid="{FDB1E1E6-ADD8-4564-8753-565B078034C8}"/>
+    <hyperlink ref="D87" r:id="rId43" xr:uid="{D469BF19-F67A-4157-A0FF-1AA4B9E0BF23}"/>
+    <hyperlink ref="D35" r:id="rId44" xr:uid="{D2E0A897-D81C-4125-9C47-3A8C879089DB}"/>
+    <hyperlink ref="C35" r:id="rId45" xr:uid="{B62AA879-0896-4DFB-BBCE-B7490B146B3E}"/>
+    <hyperlink ref="C87" r:id="rId46" xr:uid="{9F59640A-1CEF-4A8B-B161-21254F4837CD}"/>
+    <hyperlink ref="D92" r:id="rId47" xr:uid="{863F960F-332F-4E54-B6FE-24604DF43AE0}"/>
+    <hyperlink ref="D47" r:id="rId48" xr:uid="{1625DFE4-6C48-4A82-8811-F4EEB64C2D2F}"/>
+    <hyperlink ref="C47" r:id="rId49" xr:uid="{7C99B3A7-0A0D-4CE1-93C6-1839F51BF301}"/>
+    <hyperlink ref="C92" r:id="rId50" xr:uid="{450BC70E-87BA-43CB-B09E-27FB7290B23E}"/>
+    <hyperlink ref="D52" r:id="rId51" xr:uid="{968FB6ED-3EE3-4000-9ED4-DED4170844E0}"/>
+    <hyperlink ref="D53" r:id="rId52" xr:uid="{F95FFAFA-D649-4148-ACBF-893459976BA3}"/>
+    <hyperlink ref="D28" r:id="rId53" xr:uid="{867A5CA1-DED0-4BC8-AA9D-0AC38C76154A}"/>
+    <hyperlink ref="C28" r:id="rId54" xr:uid="{33C23722-2292-452E-A86A-F2FF5F22AC03}"/>
+    <hyperlink ref="C17" r:id="rId55" xr:uid="{F89D664A-980E-4238-B48D-9E9A504E1383}"/>
+    <hyperlink ref="C104" r:id="rId56" xr:uid="{51C929CE-DB05-4DB6-84D8-85DAEC31CA86}"/>
+    <hyperlink ref="C105" r:id="rId57" xr:uid="{9F47A25C-362F-482B-B273-28CEF5F32C42}"/>
+    <hyperlink ref="C106" r:id="rId58" xr:uid="{64711161-99CC-43DD-9210-5E37A90E2DC5}"/>
+    <hyperlink ref="C107" r:id="rId59" xr:uid="{DF29EEE0-9F8D-4CF7-A923-7DC294F875C1}"/>
+    <hyperlink ref="C108" r:id="rId60" xr:uid="{81445D97-055E-4976-A30D-35BCE81CA70D}"/>
+    <hyperlink ref="D110" r:id="rId61" xr:uid="{693DB290-21F0-4514-9B8B-A8622C7B663B}"/>
+    <hyperlink ref="C112" r:id="rId62" xr:uid="{D55A67DC-BCF5-42B3-A86F-2339F8569063}"/>
+    <hyperlink ref="F112" r:id="rId63" display="mailto:career@albany.edu" xr:uid="{3D51B50C-49E6-4748-8F93-05F06C5C84BC}"/>
+    <hyperlink ref="C119" r:id="rId64" xr:uid="{FCB186DB-E4AB-43E4-9D1F-D223B2641022}"/>
+    <hyperlink ref="D123" r:id="rId65" xr:uid="{480FDF2F-7B59-4251-810C-73628BB15F67}"/>
+    <hyperlink ref="D125" r:id="rId66" xr:uid="{782AF740-7E61-4A73-AC61-FACCA8448159}"/>
+    <hyperlink ref="D129" r:id="rId67" xr:uid="{E8D15C86-B9A2-49FC-8FBA-DD6355B5091B}"/>
+    <hyperlink ref="C126" r:id="rId68" xr:uid="{604F38FE-1039-4EE3-8E74-8165B8FF8430}"/>
+    <hyperlink ref="C127" r:id="rId69" xr:uid="{F0014F07-00B7-439A-9BE1-6BAE3ECD85AC}"/>
+    <hyperlink ref="C128" r:id="rId70" xr:uid="{82004575-EEEF-4DDF-972C-9340A1AA43F5}"/>
+    <hyperlink ref="C125" r:id="rId71" xr:uid="{74182992-2721-4728-8FE1-43CF72383D38}"/>
+    <hyperlink ref="C129" r:id="rId72" xr:uid="{7EBFD176-16F3-4D24-9E15-870D3D96750B}"/>
+    <hyperlink ref="F141" r:id="rId73" xr:uid="{0F9AD5BE-0C46-4CBA-ABED-01801389D4B4}"/>
+    <hyperlink ref="C141" r:id="rId74" xr:uid="{7488EE3C-4876-41B7-AD1C-E59148EF5C60}"/>
+    <hyperlink ref="F143" r:id="rId75" xr:uid="{94D425E2-BDB7-40FE-AC8D-A0E405381B9B}"/>
+    <hyperlink ref="C143" r:id="rId76" xr:uid="{8771AA61-5955-4023-916F-EA0D148D2A7D}"/>
+    <hyperlink ref="F142" r:id="rId77" xr:uid="{6E99B26B-E909-48C3-BA3B-0EEAB27C601B}"/>
+    <hyperlink ref="C142" r:id="rId78" xr:uid="{EEB16B9A-E1D2-47F9-8980-91086F1C74C7}"/>
+    <hyperlink ref="F139" r:id="rId79" xr:uid="{68D944DA-C5C2-4839-8C79-F0953BD9134E}"/>
+    <hyperlink ref="C139" r:id="rId80" xr:uid="{E8AB3E9D-8C94-415D-AB28-D7CA4C6F6343}"/>
+    <hyperlink ref="F140" r:id="rId81" xr:uid="{F3CC3505-39D1-4EEA-8FA9-8AAB6F9BF146}"/>
+    <hyperlink ref="C140" r:id="rId82" xr:uid="{7A6FF923-3DFA-4E0B-A15D-03D091C92A64}"/>
+    <hyperlink ref="C131" r:id="rId83" xr:uid="{1FA6BB05-074A-4060-BBBF-C2C63D7C12FC}"/>
+    <hyperlink ref="F130" r:id="rId84" xr:uid="{59790EAE-256A-42B0-A297-EC57CF947976}"/>
+    <hyperlink ref="F132" r:id="rId85" xr:uid="{F171B7C9-73EF-4309-8CB2-15FCE8C2CC9E}"/>
+    <hyperlink ref="D127" r:id="rId86" xr:uid="{AE4C7754-0BC6-4329-BE3F-677BC8B998A9}"/>
+    <hyperlink ref="D136" r:id="rId87" xr:uid="{9B78D813-C58E-43B6-93FE-BA5C85BE774B}"/>
+    <hyperlink ref="C135" r:id="rId88" xr:uid="{5EA92CD5-A670-4F7D-BE25-D144C30E8390}"/>
+    <hyperlink ref="C136" r:id="rId89" xr:uid="{04A96344-FBF4-45CD-BF8A-74E2E9E7A1D4}"/>
+    <hyperlink ref="D138" r:id="rId90" xr:uid="{E6E27C26-8B3F-4E6E-A7F0-56D080F5A059}"/>
+    <hyperlink ref="D145" r:id="rId91" xr:uid="{72104B61-6124-4681-83A2-C04FE8A81422}"/>
+    <hyperlink ref="D150" r:id="rId92" xr:uid="{E34F98A6-233F-4D98-AA31-6A6F8739EE10}"/>
+    <hyperlink ref="F150" r:id="rId93" xr:uid="{F2B73996-B1DF-4B50-B7BF-4A8DAC2EBCF8}"/>
+    <hyperlink ref="D151" r:id="rId94" xr:uid="{E9C2E3C3-D837-4EED-B479-25B788589D5C}"/>
+    <hyperlink ref="F152" r:id="rId95" xr:uid="{B8E43DA3-B50D-4D55-8A39-449316C19072}"/>
+    <hyperlink ref="D152" r:id="rId96" xr:uid="{93C67D5A-182E-44E5-98F0-C26DAA38348E}"/>
+    <hyperlink ref="D153" r:id="rId97" xr:uid="{EB6504E0-5D02-48B9-AA8E-AD172B0786CC}"/>
+    <hyperlink ref="F154" r:id="rId98" xr:uid="{F6FEA5C8-2D79-4B3D-8A2D-56E7162EDEEF}"/>
+    <hyperlink ref="D154" r:id="rId99" xr:uid="{5E9ADF47-E415-42D0-96AD-AC14CEFDB46A}"/>
+    <hyperlink ref="C145" r:id="rId100" xr:uid="{8F9F1B99-EA6C-4B9C-A2F0-0A5ADEB1AAC5}"/>
+    <hyperlink ref="C146" r:id="rId101" xr:uid="{7DDADF0B-37EF-456E-A584-90A75DC8E532}"/>
+    <hyperlink ref="C147" r:id="rId102" xr:uid="{4DBCE484-8796-477B-9C75-E13EC16BE78D}"/>
+    <hyperlink ref="C148" r:id="rId103" xr:uid="{4B652928-E776-4C62-81AB-B3F682C91A9B}"/>
+    <hyperlink ref="C149" r:id="rId104" xr:uid="{263071B5-2297-41D5-BD0E-1DD5BC8884ED}"/>
+    <hyperlink ref="D146:D149" r:id="rId105" display="https://www.risse-albany.org/" xr:uid="{281154D0-8EC0-4929-9B07-64C9F15DC597}"/>
+    <hyperlink ref="C150" r:id="rId106" xr:uid="{B16923BE-F0C3-427E-9F10-6F9A519FC287}"/>
+    <hyperlink ref="C152" r:id="rId107" xr:uid="{E132F971-9DCB-4C0F-937B-6476DE4ACCAD}"/>
+    <hyperlink ref="C153" r:id="rId108" xr:uid="{A00E4B55-C978-401C-8846-DB1632284D50}"/>
+    <hyperlink ref="C154" r:id="rId109" xr:uid="{7C2DE1D7-47ED-40CF-937D-415B2488F028}"/>
+    <hyperlink ref="C156" r:id="rId110" xr:uid="{B28590EE-4458-4CAE-AE78-9975E73BC873}"/>
+    <hyperlink ref="D156" r:id="rId111" xr:uid="{1E66DBCC-AB5E-4E32-804B-D7193FA752EE}"/>
+    <hyperlink ref="F118" r:id="rId112" xr:uid="{7369515B-3200-4C5D-8DBA-683E7EA7089D}"/>
+    <hyperlink ref="F155" r:id="rId113" xr:uid="{F7A76B19-1F37-4DF5-BD65-E0CE94052793}"/>
+    <hyperlink ref="C159" r:id="rId114" display="tel:518-442-3943" xr:uid="{FF797009-0F9E-2A4A-A3A7-106BF4E6C3BA}"/>
+    <hyperlink ref="C158" r:id="rId115" xr:uid="{39AC894D-928D-1945-B205-EC44DA75AA2F}"/>
+    <hyperlink ref="F159" r:id="rId116" display="mailto:passmentor@albany.edu" xr:uid="{92FF97A4-6BFD-2047-AFAC-29DC3A1B4E54}"/>
+    <hyperlink ref="D162" r:id="rId117" xr:uid="{3DE194FC-17EE-A649-8859-317715F43009}"/>
+    <hyperlink ref="F160" r:id="rId118" display="mailto:info@cdphpcycle.org" xr:uid="{C1021047-F2A6-0D44-921E-65780A9C7407}"/>
+    <hyperlink ref="D160" r:id="rId119" xr:uid="{0F5D7C84-6C50-814B-95E8-D5E467CA24AF}"/>
+    <hyperlink ref="C166" r:id="rId120" xr:uid="{690FD66A-CACE-F148-B4D1-FC887F23F5EC}"/>
+    <hyperlink ref="C167" r:id="rId121" xr:uid="{DA09BFEF-E59D-A74C-9D84-99944ED51719}"/>
+    <hyperlink ref="C168" r:id="rId122" xr:uid="{EF917863-B783-6746-BA4E-0B21880445D2}"/>
+    <hyperlink ref="C169" r:id="rId123" xr:uid="{D678F8DB-2E76-8645-8492-668ADDB70C30}"/>
+    <hyperlink ref="D169" r:id="rId124" xr:uid="{5539CF43-9824-C040-831E-11780C081C68}"/>
+    <hyperlink ref="D168" r:id="rId125" xr:uid="{9FF172EE-8CFA-AB47-93A1-C78BEC3D269B}"/>
+    <hyperlink ref="D167" r:id="rId126" xr:uid="{19A9ABBB-6357-F847-AEED-C41F8DD723D5}"/>
+    <hyperlink ref="D166" r:id="rId127" xr:uid="{572C4F40-4005-884C-965A-3699D5D51DD3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId132"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId128"/>
 </worksheet>
 </file>